--- a/fertilidade/AEAdubacao.xlsx
+++ b/fertilidade/AEAdubacao.xlsx
@@ -211,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -260,6 +260,7 @@
     </xf>
     <xf numFmtId="2" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -298,7 +299,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -590,6 +591,9 @@
     <author>Fonte</author>
     <author>Referência técnica</author>
     <author>Nota</author>
+    <author>Usado na aba Soja</author>
+    <author>Usado nas abas Milho e Outras Culturas</author>
+    <author>Usado nas abas Soja, Milho e Outras Culturas</author>
   </authors>
   <commentList>
     <comment ref="C19" authorId="0" shapeId="0">
@@ -605,6 +609,26 @@
     <comment ref="C42" authorId="2" shapeId="0">
       <text>
         <t>Na convertido de mg/dm³ para mmolc/dm³ dividindo por 23 (massa atômica do sódio).</t>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="3" shapeId="0">
+      <text>
+        <t>Soja bem inoculada não responde economicamente a N mineral (Embrapa Soja). Se 'Não', a Soja calcula N por exportação/eficiência, igual ao milho.</t>
+      </text>
+    </comment>
+    <comment ref="C50" authorId="4" shapeId="0">
+      <text>
+        <t>Concede um crédito de 25 kg N/ha quando a cultura antecessora foi leguminosa bem nodulada.</t>
+      </text>
+    </comment>
+    <comment ref="C51" authorId="4" shapeId="0">
+      <text>
+        <t>Eficiência típica de recuperação de N por gramíneas em campo (perdas por volatilização, lixiviação, desnitrificação). Editável - Confiança Média.</t>
+      </text>
+    </comment>
+    <comment ref="C52" authorId="5" shapeId="0">
+      <text>
+        <t>Eficiência padrão de aproveitamento do enxofre aplicado. Editável - Confiança Média.</t>
       </text>
     </comment>
   </commentList>
@@ -659,12 +683,78 @@
 <file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Premissa</author>
+    <author>Fonte completa</author>
+    <author>Confiança - detalhe</author>
   </authors>
   <commentList>
-    <comment ref="C28" authorId="0" shapeId="0">
+    <comment ref="S6" authorId="0" shapeId="0">
       <text>
-        <t>Eficiência típica de recuperação de N por gramíneas em condições de campo (perdas por volatilização de ureia, lixiviação, desnitrificação). Valor editável - Confiança Média.</t>
+        <t>Sfredo, G.J. Soja no Brasil: calagem, adubação e nutrição mineral. Documentos 305, Embrapa Soja, 2008; valores consolidados também em Malavolta (2006) e boletins técnicos de manejo de fertilidade.</t>
+      </text>
+    </comment>
+    <comment ref="T6" authorId="1" shapeId="0">
+      <text>
+        <t>Média (variação relevante relatada entre fontes, sobretudo para K em altas produtividades - efeito de diluição já discutido por Zanon et al. em curvas de resposta a potássio).</t>
+      </text>
+    </comment>
+    <comment ref="S7" authorId="0" shapeId="0">
+      <text>
+        <t>Coelho, A.M. Nutrição e Adubação do Milho. Circular Técnica 78, Embrapa Milho e Sorgo, 2006 (valores 'clássicos' de exportação pelo grão).</t>
+      </text>
+    </comment>
+    <comment ref="T7" authorId="1" shapeId="0">
+      <text>
+        <t>Média (circulares mais recentes revisam alguns coeficientes; verificar se tratam de grão isolado ou planta inteira/silagem antes de adotar valores diferentes).</t>
+      </text>
+    </comment>
+    <comment ref="S8" authorId="0" shapeId="0">
+      <text>
+        <t>Valores de referência consolidados na prática agronômica (perfil nutricional próximo ao do milho, cultura de mesma família); ajustar com boletim regional (Embrapa Milho e Sorgo) quando disponível.</t>
+      </text>
+    </comment>
+    <comment ref="T8" authorId="1" shapeId="0">
+      <text>
+        <t>Baixa-Média</t>
+      </text>
+    </comment>
+    <comment ref="S9" authorId="0" shapeId="0">
+      <text>
+        <t>Valores de referência consolidados na prática agronômica brasileira (perfil leguminosa, próximo à soja em proporção, porém com ciclo mais curto e menor fixação biológica líquida). Ajustar com boletim regional (IAC/Embrapa Arroz e Feijão) quando disponível.</t>
+      </text>
+    </comment>
+    <comment ref="T9" authorId="1" shapeId="0">
+      <text>
+        <t>Baixa-Média</t>
+      </text>
+    </comment>
+    <comment ref="S10" authorId="0" shapeId="0">
+      <text>
+        <t>Valores de referência consolidados na prática agronômica (exportação por tonelada de colmo); ajustar com Boletim 200/Fundação MT ou boletim regional do setor sucroenergético quando disponível.</t>
+      </text>
+    </comment>
+    <comment ref="T10" authorId="1" shapeId="0">
+      <text>
+        <t>Baixa-Média</t>
+      </text>
+    </comment>
+    <comment ref="S11" authorId="0" shapeId="0">
+      <text>
+        <t>Valores de referência consolidados na prática agronômica para exportação por tonelada de matéria seca em pastagens tropicais (Panicum maximum); ajustar com boletim regional (Embrapa Gado de Corte) quando disponível.</t>
+      </text>
+    </comment>
+    <comment ref="T11" authorId="1" shapeId="0">
+      <text>
+        <t>Baixa-Média</t>
+      </text>
+    </comment>
+    <comment ref="S12" authorId="0" shapeId="0">
+      <text>
+        <t>Valores de referência consolidados na prática agronômica para exportação por tonelada de matéria seca em pastagens tropicais (Brachiaria/Urochloa spp.); ajustar com boletim regional (Embrapa Gado de Corte) quando disponível.</t>
+      </text>
+    </comment>
+    <comment ref="T12" authorId="1" shapeId="0">
+      <text>
+        <t>Baixa-Média</t>
       </text>
     </comment>
   </commentList>
@@ -1398,18 +1488,18 @@
           <t>Cultura selecionada em Dados de Entrada</t>
         </is>
       </c>
-      <c r="C4" s="38">
+      <c r="C4" s="39">
         <f>'Dados de Entrada'!C8</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Alerta</t>
         </is>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>IF(C4&lt;&gt;"Milho","A cultura em Dados de Entrada não é Milho - ajuste antes de usar esta aba","OK")</f>
         <v/>
       </c>
@@ -1420,7 +1510,7 @@
           <t>Área (ha)</t>
         </is>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="56">
         <f>'Dados de Entrada'!C7</f>
         <v/>
       </c>
@@ -1431,7 +1521,7 @@
           <t>Produtividade esperada</t>
         </is>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="38">
         <f>'Dados de Entrada'!C9</f>
         <v/>
       </c>
@@ -1442,7 +1532,7 @@
           <t>Unidade</t>
         </is>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="39">
         <f>'Dados de Entrada'!C10</f>
         <v/>
       </c>
@@ -1453,7 +1543,7 @@
           <t>Classe textural</t>
         </is>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="39">
         <f>'Dados de Entrada'!C19</f>
         <v/>
       </c>
@@ -1464,7 +1554,7 @@
           <t>Matéria Orgânica (g/dm³)</t>
         </is>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="33">
         <f>'Dados de Entrada'!E25</f>
         <v/>
       </c>
@@ -1475,18 +1565,18 @@
           <t>Sistema de plantio</t>
         </is>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="39">
         <f>'Dados de Entrada'!C12</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="41" t="inlineStr">
+      <c r="B12" s="42" t="inlineStr">
         <is>
           <t>Produtividade meta em t/ha</t>
         </is>
       </c>
-      <c r="C12" s="56">
+      <c r="C12" s="57">
         <f>C7*VLOOKUP("Milho",TAB_CULTURAS,3,FALSE)/1000</f>
         <v/>
       </c>
@@ -1504,7 +1594,7 @@
           <t>Classe - Fósforo</t>
         </is>
       </c>
-      <c r="C15" s="57">
+      <c r="C15" s="58">
         <f>Interpretação!E6</f>
         <v/>
       </c>
@@ -1515,7 +1605,7 @@
           <t>Classe - Potássio</t>
         </is>
       </c>
-      <c r="C16" s="57">
+      <c r="C16" s="58">
         <f>Interpretação!E7</f>
         <v/>
       </c>
@@ -1526,7 +1616,7 @@
           <t>Classe - Cálcio</t>
         </is>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="58">
         <f>Interpretação!E8</f>
         <v/>
       </c>
@@ -1537,7 +1627,7 @@
           <t>Classe - Magnésio</t>
         </is>
       </c>
-      <c r="C18" s="57">
+      <c r="C18" s="58">
         <f>Interpretação!E9</f>
         <v/>
       </c>
@@ -1548,7 +1638,7 @@
           <t>Classe - Enxofre</t>
         </is>
       </c>
-      <c r="C19" s="57">
+      <c r="C19" s="58">
         <f>Interpretação!E12</f>
         <v/>
       </c>
@@ -1559,7 +1649,7 @@
           <t>Classe - Zinco</t>
         </is>
       </c>
-      <c r="C20" s="57">
+      <c r="C20" s="58">
         <f>Interpretação!E13</f>
         <v/>
       </c>
@@ -1570,7 +1660,7 @@
           <t>Classe - Boro</t>
         </is>
       </c>
-      <c r="C21" s="57">
+      <c r="C21" s="58">
         <f>Interpretação!E17</f>
         <v/>
       </c>
@@ -1581,7 +1671,7 @@
           <t>Classe - Cobre</t>
         </is>
       </c>
-      <c r="C22" s="57">
+      <c r="C22" s="58">
         <f>Interpretação!E14</f>
         <v/>
       </c>
@@ -1592,7 +1682,7 @@
           <t>Classe - Manganês</t>
         </is>
       </c>
-      <c r="C23" s="57">
+      <c r="C23" s="58">
         <f>Interpretação!E15</f>
         <v/>
       </c>
@@ -1603,7 +1693,7 @@
           <t>Classe - Molibdênio</t>
         </is>
       </c>
-      <c r="C24" s="57">
+      <c r="C24" s="58">
         <f>Interpretação!E18</f>
         <v/>
       </c>
@@ -1618,23 +1708,23 @@
     <row r="27">
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Cultura anterior foi leguminosa (crédito de N)?</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
+          <t>Cultura anterior foi leguminosa? (Dados de Entrada)</t>
+        </is>
+      </c>
+      <c r="C27" s="39">
+        <f>'Dados de Entrada'!C50</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Eficiência de aproveitamento do N (%)</t>
-        </is>
-      </c>
-      <c r="C28" s="60" t="n">
-        <v>0.6</v>
+          <t>Eficiência de aproveitamento do N (%) (Dados de Entrada)</t>
+        </is>
+      </c>
+      <c r="C28" s="61">
+        <f>'Dados de Entrada'!C51</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1643,24 +1733,24 @@
           <t>Exportação de N pela produtividade meta (kg/ha)</t>
         </is>
       </c>
-      <c r="C29" s="49">
+      <c r="C29" s="50">
         <f>C12*VLOOKUP("Milho",TAB_CULTURAS,5,FALSE)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="41" t="inlineStr">
+      <c r="B30" s="42" t="inlineStr">
         <is>
           <t>Nitrogênio recomendado (kg N/ha)</t>
         </is>
       </c>
-      <c r="C30" s="58">
+      <c r="C30" s="59">
         <f>MAX(0,C29/C28-IF(C27="Sim",25,0))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="30" t="inlineStr">
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>Fonte/Confiança: Média - dose de manutenção por exportação/eficiência, com crédito de N de 25 kg/ha quando a cultura anterior foi leguminosa bem nodulada (estimativa de uso corrente). Não substitui curva de resposta a N calibrada localmente (solo, clima, híbrido).</t>
         </is>
@@ -1681,7 +1771,7 @@
           <t>Exportação pela produtividade meta (kg/ha)</t>
         </is>
       </c>
-      <c r="C36" s="49">
+      <c r="C36" s="50">
         <f>C12*VLOOKUP("Milho",TAB_CULTURAS,6,FALSE)</f>
         <v/>
       </c>
@@ -1692,7 +1782,7 @@
           <t>Eficiência de aproveitamento do fertilizante (%)</t>
         </is>
       </c>
-      <c r="C37" s="59">
+      <c r="C37" s="60">
         <f>VLOOKUP(C9,TAB_EFICIENCIA,2,FALSE)</f>
         <v/>
       </c>
@@ -1703,7 +1793,7 @@
           <t>Dose de manutenção (exportação / eficiência), kg/ha</t>
         </is>
       </c>
-      <c r="C38" s="49">
+      <c r="C38" s="50">
         <f>C36/C37</f>
         <v/>
       </c>
@@ -1714,7 +1804,7 @@
           <t>Classe de fertilidade considerada</t>
         </is>
       </c>
-      <c r="C39" s="57">
+      <c r="C39" s="58">
         <f>C15</f>
         <v/>
       </c>
@@ -1725,18 +1815,18 @@
           <t>Fator de ajuste por classe (construção/manutenção/redução)</t>
         </is>
       </c>
-      <c r="C40" s="44">
+      <c r="C40" s="45">
         <f>VLOOKUP(C15,TAB_FATOR_CLASSE,2,FALSE)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="41" t="inlineStr">
+      <c r="B41" s="42" t="inlineStr">
         <is>
           <t>Dose final de P2O5 (kg/ha)</t>
         </is>
       </c>
-      <c r="C41" s="58">
+      <c r="C41" s="59">
         <f>C38*C40</f>
         <v/>
       </c>
@@ -1747,13 +1837,13 @@
           <t>Total para a área (kg)</t>
         </is>
       </c>
-      <c r="C42" s="52">
+      <c r="C42" s="53">
         <f>C41*C6</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="30" t="inlineStr">
+      <c r="B43" s="31" t="inlineStr">
         <is>
           <t>Modelo: dose = (exportação pelo grão na produtividade meta / eficiência de aproveitamento pela textura) x fator de ajuste pela classe de fertilidade atual do solo. Não é uma tabela fixa - recalcula a cada mudança de solo, textura ou produtividade. Fonte dos coeficientes de exportação: ver aba BD Culturas. Confiança do fator de ajuste: Média (premissa transparente e editável).</t>
         </is>
@@ -1774,7 +1864,7 @@
           <t>Exportação pela produtividade meta (kg/ha)</t>
         </is>
       </c>
-      <c r="C48" s="49">
+      <c r="C48" s="50">
         <f>C12*VLOOKUP("Milho",TAB_CULTURAS,7,FALSE)</f>
         <v/>
       </c>
@@ -1785,7 +1875,7 @@
           <t>Eficiência de aproveitamento do fertilizante (%)</t>
         </is>
       </c>
-      <c r="C49" s="59">
+      <c r="C49" s="60">
         <f>VLOOKUP(C9,TAB_EFICIENCIA,3,FALSE)</f>
         <v/>
       </c>
@@ -1796,7 +1886,7 @@
           <t>Dose de manutenção (exportação / eficiência), kg/ha</t>
         </is>
       </c>
-      <c r="C50" s="49">
+      <c r="C50" s="50">
         <f>C48/C49</f>
         <v/>
       </c>
@@ -1807,7 +1897,7 @@
           <t>Classe de fertilidade considerada</t>
         </is>
       </c>
-      <c r="C51" s="57">
+      <c r="C51" s="58">
         <f>C16</f>
         <v/>
       </c>
@@ -1818,18 +1908,18 @@
           <t>Fator de ajuste por classe (construção/manutenção/redução)</t>
         </is>
       </c>
-      <c r="C52" s="44">
+      <c r="C52" s="45">
         <f>VLOOKUP(C16,TAB_FATOR_CLASSE,2,FALSE)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="41" t="inlineStr">
+      <c r="B53" s="42" t="inlineStr">
         <is>
           <t>Dose final de K2O (kg/ha)</t>
         </is>
       </c>
-      <c r="C53" s="58">
+      <c r="C53" s="59">
         <f>C50*C52</f>
         <v/>
       </c>
@@ -1840,13 +1930,13 @@
           <t>Total para a área (kg)</t>
         </is>
       </c>
-      <c r="C54" s="52">
+      <c r="C54" s="53">
         <f>C53*C6</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="30" t="inlineStr">
+      <c r="B55" s="31" t="inlineStr">
         <is>
           <t>Modelo: dose = (exportação pelo grão na produtividade meta / eficiência de aproveitamento pela textura) x fator de ajuste pela classe de fertilidade atual do solo. Não é uma tabela fixa - recalcula a cada mudança de solo, textura ou produtividade. Fonte dos coeficientes de exportação: ver aba BD Culturas. Confiança do fator de ajuste: Média (premissa transparente e editável).</t>
         </is>
@@ -1867,7 +1957,7 @@
           <t>Exportação de S pela produtividade meta (kg/ha)</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>C12*VLOOKUP("Milho",TAB_CULTURAS,8,FALSE)</f>
         <v/>
       </c>
@@ -1875,11 +1965,12 @@
     <row r="61">
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Eficiência de aproveitamento do S (%) - padrão</t>
-        </is>
-      </c>
-      <c r="C61" s="60" t="n">
-        <v>0.6</v>
+          <t>Eficiência de aproveitamento do S (%) (Dados de Entrada)</t>
+        </is>
+      </c>
+      <c r="C61" s="61">
+        <f>'Dados de Entrada'!C52</f>
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -1888,24 +1979,24 @@
           <t>Fator de ajuste por classe de S</t>
         </is>
       </c>
-      <c r="C62" s="44">
+      <c r="C62" s="45">
         <f>VLOOKUP(C19,TAB_FATOR_CLASSE,2,FALSE)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="41" t="inlineStr">
+      <c r="B63" s="42" t="inlineStr">
         <is>
           <t>Dose final de S (kg/ha)</t>
         </is>
       </c>
-      <c r="C63" s="58">
+      <c r="C63" s="59">
         <f>C60/C61*C62</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="43" t="inlineStr">
+      <c r="B64" s="44" t="inlineStr">
         <is>
           <t>Parte do S já pode ser suprida via gesso agrícola (ver aba Gessagem) - evitar dupla contagem ao montar a mistura final.</t>
         </is>
@@ -1924,7 +2015,7 @@
           <t>Exportação de Ca pela produtividade meta (kg/ha)</t>
         </is>
       </c>
-      <c r="C67" s="49">
+      <c r="C67" s="50">
         <f>C12*VLOOKUP("Milho",TAB_CULTURAS,9,FALSE)</f>
         <v/>
       </c>
@@ -1935,13 +2026,13 @@
           <t>Exportação de Mg pela produtividade meta (kg/ha)</t>
         </is>
       </c>
-      <c r="C68" s="49">
+      <c r="C68" s="50">
         <f>C12*VLOOKUP("Milho",TAB_CULTURAS,10,FALSE)</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="43" t="inlineStr">
+      <c r="B69" s="44" t="inlineStr">
         <is>
           <t>Ver abas Calagem e Gessagem para a recomendação de correção de Ca e Mg via calcário/gesso.</t>
         </is>
@@ -1960,7 +2051,7 @@
           <t>Zn - dose via solo (kg/ha produto puro)</t>
         </is>
       </c>
-      <c r="C72" s="44">
+      <c r="C72" s="45">
         <f>IFERROR(VLOOKUP("Zn|"&amp;C20,TAB_MICRO_DOSE,4,FALSE),0)</f>
         <v/>
       </c>
@@ -1971,7 +2062,7 @@
           <t>B - dose via solo (kg/ha produto puro)</t>
         </is>
       </c>
-      <c r="C73" s="44">
+      <c r="C73" s="45">
         <f>IFERROR(VLOOKUP("B|"&amp;C21,TAB_MICRO_DOSE,4,FALSE),0)</f>
         <v/>
       </c>
@@ -1982,7 +2073,7 @@
           <t>Cu - dose via solo (kg/ha produto puro)</t>
         </is>
       </c>
-      <c r="C74" s="44">
+      <c r="C74" s="45">
         <f>IFERROR(VLOOKUP("Cu|"&amp;C22,TAB_MICRO_DOSE,4,FALSE),0)</f>
         <v/>
       </c>
@@ -1993,7 +2084,7 @@
           <t>Mn - dose via solo (kg/ha produto puro)</t>
         </is>
       </c>
-      <c r="C75" s="44">
+      <c r="C75" s="45">
         <f>IFERROR(VLOOKUP("Mn|"&amp;C23,TAB_MICRO_DOSE,4,FALSE),0)</f>
         <v/>
       </c>
@@ -2004,7 +2095,7 @@
           <t>Mo - dose via solo (kg/ha produto puro)</t>
         </is>
       </c>
-      <c r="C76" s="44">
+      <c r="C76" s="45">
         <f>IFERROR(VLOOKUP("Mo|"&amp;C24,TAB_MICRO_DOSE,4,FALSE),0)</f>
         <v/>
       </c>
@@ -2039,11 +2130,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="C80" s="44">
+      <c r="C80" s="45">
         <f>C30</f>
         <v/>
       </c>
-      <c r="D80" s="52">
+      <c r="D80" s="53">
         <f>C30*C6</f>
         <v/>
       </c>
@@ -2054,11 +2145,11 @@
           <t>P2O5</t>
         </is>
       </c>
-      <c r="C81" s="44">
+      <c r="C81" s="45">
         <f>C41</f>
         <v/>
       </c>
-      <c r="D81" s="52">
+      <c r="D81" s="53">
         <f>C41*C6</f>
         <v/>
       </c>
@@ -2069,11 +2160,11 @@
           <t>K2O</t>
         </is>
       </c>
-      <c r="C82" s="44">
+      <c r="C82" s="45">
         <f>C53</f>
         <v/>
       </c>
-      <c r="D82" s="52">
+      <c r="D82" s="53">
         <f>C53*C6</f>
         <v/>
       </c>
@@ -2084,11 +2175,11 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C83" s="44">
+      <c r="C83" s="45">
         <f>C63</f>
         <v/>
       </c>
-      <c r="D83" s="52">
+      <c r="D83" s="53">
         <f>C63*C6</f>
         <v/>
       </c>
@@ -2099,11 +2190,11 @@
           <t>Zn</t>
         </is>
       </c>
-      <c r="C84" s="44">
+      <c r="C84" s="45">
         <f>C72</f>
         <v/>
       </c>
-      <c r="D84" s="52">
+      <c r="D84" s="53">
         <f>C72*C6</f>
         <v/>
       </c>
@@ -2114,11 +2205,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="C85" s="44">
+      <c r="C85" s="45">
         <f>C73</f>
         <v/>
       </c>
-      <c r="D85" s="52">
+      <c r="D85" s="53">
         <f>C73*C6</f>
         <v/>
       </c>
@@ -2129,11 +2220,11 @@
           <t>Cu</t>
         </is>
       </c>
-      <c r="C86" s="44">
+      <c r="C86" s="45">
         <f>C74</f>
         <v/>
       </c>
-      <c r="D86" s="52">
+      <c r="D86" s="53">
         <f>C74*C6</f>
         <v/>
       </c>
@@ -2144,11 +2235,11 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="C87" s="44">
+      <c r="C87" s="45">
         <f>C75</f>
         <v/>
       </c>
-      <c r="D87" s="52">
+      <c r="D87" s="53">
         <f>C75*C6</f>
         <v/>
       </c>
@@ -2159,11 +2250,11 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="C88" s="44">
+      <c r="C88" s="45">
         <f>C76</f>
         <v/>
       </c>
-      <c r="D88" s="52">
+      <c r="D88" s="53">
         <f>C76*C6</f>
         <v/>
       </c>
@@ -2187,13 +2278,7 @@
     <mergeCell ref="B64:G64"/>
     <mergeCell ref="B69:G69"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Sim,Não"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2203,7 +2288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E32"/>
+  <dimension ref="B1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2221,7 +2306,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Módulo simplificado (Fase 1): calcula a adubação de manutenção pela exportação de nutrientes na produtividade meta, ajustada pela eficiência de aproveitamento (textura do solo) - sem o fator de ajuste fino por classe de fertilidade usado em Soja/Milho e sem curva de resposta específica. Use como referência inicial; para essas culturas recomenda-se complementar com boletim regional (Embrapa Milho e Sorgo, Embrapa Arroz e Feijão, Fundação MT/Boletim 200, Embrapa Gado de Corte) conforme a cultura selecionada.</t>
         </is>
@@ -2242,18 +2327,18 @@
           <t>Cultura selecionada em Dados de Entrada</t>
         </is>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="39">
         <f>'Dados de Entrada'!C8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B9" s="44" t="inlineStr">
         <is>
           <t>Alerta</t>
         </is>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>IF(OR(C8="Soja",C8="Milho"),"Soja e Milho têm abas dedicadas com motor completo - use-as no lugar desta",IF(OR(C8="Sorgo",C8="Feijão",C8="Cana-de-açúcar",C8="Pastagem Panicum",C8="Pastagem Brachiaria"),"OK","Cultura não reconhecida"))</f>
         <v/>
       </c>
@@ -2264,7 +2349,7 @@
           <t>Área (ha)</t>
         </is>
       </c>
-      <c r="C10" s="55">
+      <c r="C10" s="56">
         <f>'Dados de Entrada'!C7</f>
         <v/>
       </c>
@@ -2275,7 +2360,7 @@
           <t>Produtividade esperada</t>
         </is>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="38">
         <f>'Dados de Entrada'!C9</f>
         <v/>
       </c>
@@ -2286,7 +2371,7 @@
           <t>Unidade</t>
         </is>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="39">
         <f>'Dados de Entrada'!C10</f>
         <v/>
       </c>
@@ -2297,18 +2382,18 @@
           <t>Classe textural</t>
         </is>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="39">
         <f>'Dados de Entrada'!C19</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="41" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>Produtividade meta convertida (t/ha ou t MS/ha)</t>
         </is>
       </c>
-      <c r="C14" s="56">
+      <c r="C14" s="57">
         <f>C11*VLOOKUP(C8,TAB_CULTURAS,3,FALSE)/1000</f>
         <v/>
       </c>
@@ -2326,7 +2411,7 @@
           <t>Eficiência P (%) - conforme textura</t>
         </is>
       </c>
-      <c r="C17" s="59">
+      <c r="C17" s="60">
         <f>VLOOKUP(C13,TAB_EFICIENCIA,2,FALSE)</f>
         <v/>
       </c>
@@ -2337,7 +2422,7 @@
           <t>Eficiência K (%) - conforme textura</t>
         </is>
       </c>
-      <c r="C18" s="59">
+      <c r="C18" s="60">
         <f>VLOOKUP(C13,TAB_EFICIENCIA,3,FALSE)</f>
         <v/>
       </c>
@@ -2345,76 +2430,69 @@
     <row r="19">
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Eficiência N e S (%) - padrão geral</t>
-        </is>
-      </c>
-      <c r="C19" s="60" t="n">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
+          <t>Eficiência N (%) (Dados de Entrada)</t>
+        </is>
+      </c>
+      <c r="C19" s="61">
+        <f>'Dados de Entrada'!C51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Eficiência S (%) (Dados de Entrada)</t>
+        </is>
+      </c>
+      <c r="C20" s="61">
+        <f>'Dados de Entrada'!C52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>3. Adubação de manutenção recomendada (exportação / eficiência)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="7" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Nutriente</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Exportação (kg/ha)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Dose recomendada (kg/ha)</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Total área (kg)</t>
         </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C23" s="49">
-        <f>C14*VLOOKUP(C8,TAB_CULTURAS,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D23" s="58">
-        <f>C23/C19</f>
-        <v/>
-      </c>
-      <c r="E23" s="52">
-        <f>D23*C10</f>
-        <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>P2O5</t>
-        </is>
-      </c>
-      <c r="C24" s="49">
-        <f>C14*VLOOKUP(C8,TAB_CULTURAS,6,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D24" s="58">
-        <f>C24/C17</f>
-        <v/>
-      </c>
-      <c r="E24" s="52">
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C24" s="50">
+        <f>C14*VLOOKUP(C8,TAB_CULTURAS,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="D24" s="59">
+        <f>C24/C19</f>
+        <v/>
+      </c>
+      <c r="E24" s="53">
         <f>D24*C10</f>
         <v/>
       </c>
@@ -2422,18 +2500,18 @@
     <row r="25">
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>K2O</t>
-        </is>
-      </c>
-      <c r="C25" s="49">
-        <f>C14*VLOOKUP(C8,TAB_CULTURAS,7,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D25" s="58">
-        <f>C25/C18</f>
-        <v/>
-      </c>
-      <c r="E25" s="52">
+          <t>P2O5</t>
+        </is>
+      </c>
+      <c r="C25" s="50">
+        <f>C14*VLOOKUP(C8,TAB_CULTURAS,6,FALSE)</f>
+        <v/>
+      </c>
+      <c r="D25" s="59">
+        <f>C25/C17</f>
+        <v/>
+      </c>
+      <c r="E25" s="53">
         <f>D25*C10</f>
         <v/>
       </c>
@@ -2441,18 +2519,18 @@
     <row r="26">
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C26" s="49">
-        <f>C14*VLOOKUP(C8,TAB_CULTURAS,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D26" s="58">
-        <f>C26/C19</f>
-        <v/>
-      </c>
-      <c r="E26" s="52">
+          <t>K2O</t>
+        </is>
+      </c>
+      <c r="C26" s="50">
+        <f>C14*VLOOKUP(C8,TAB_CULTURAS,7,FALSE)</f>
+        <v/>
+      </c>
+      <c r="D26" s="59">
+        <f>C26/C18</f>
+        <v/>
+      </c>
+      <c r="E26" s="53">
         <f>D26*C10</f>
         <v/>
       </c>
@@ -2460,55 +2538,74 @@
     <row r="27">
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Ca (informativo)</t>
-        </is>
-      </c>
-      <c r="C27" s="49">
-        <f>C14*VLOOKUP(C8,TAB_CULTURAS,9,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D27" s="43" t="inlineStr">
-        <is>
-          <t>Ver Calagem/Gessagem</t>
-        </is>
-      </c>
-      <c r="E27" s="43" t="inlineStr"/>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C27" s="50">
+        <f>C14*VLOOKUP(C8,TAB_CULTURAS,8,FALSE)</f>
+        <v/>
+      </c>
+      <c r="D27" s="59">
+        <f>C27/C20</f>
+        <v/>
+      </c>
+      <c r="E27" s="53">
+        <f>D27*C10</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="8" t="inlineStr">
         <is>
+          <t>Ca (informativo)</t>
+        </is>
+      </c>
+      <c r="C28" s="50">
+        <f>C14*VLOOKUP(C8,TAB_CULTURAS,9,FALSE)</f>
+        <v/>
+      </c>
+      <c r="D28" s="44" t="inlineStr">
+        <is>
+          <t>Ver Calagem/Gessagem</t>
+        </is>
+      </c>
+      <c r="E28" s="44" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
           <t>Mg (informativo)</t>
         </is>
       </c>
-      <c r="C28" s="49">
+      <c r="C29" s="50">
         <f>C14*VLOOKUP(C8,TAB_CULTURAS,10,FALSE)</f>
         <v/>
       </c>
-      <c r="D28" s="43" t="inlineStr">
+      <c r="D29" s="44" t="inlineStr">
         <is>
           <t>Ver Calagem/Gessagem</t>
         </is>
       </c>
-      <c r="E28" s="43" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="30" t="inlineStr">
+      <c r="E29" s="44" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>Fonte dos coeficientes de exportação: ver aba BD Culturas (coluna Fonte/Confiança por cultura). Confiança geral deste módulo simplificado: Baixa-Média - adequado como estimativa inicial de manutenção, não substitui curva de resposta local nem tabela oficial por classe de solo específica da cultura.</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32"/>
+    <row r="33"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B31:E33"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B30:E32"/>
     <mergeCell ref="B3:E5"/>
+    <mergeCell ref="B22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2549,7 +2646,7 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Tabela editável. Ajuste os percentuais conforme o rótulo/garantia do produto realmente utilizado e o preço de referência (R$/t) conforme cotação local. Linhas em branco no final permitem adicionar novos produtos - basta preencher Nome e os percentuais de garantia; a aba Mistura de Fertilizantes referencia esta tabela por nome de produto.</t>
         </is>
@@ -2685,7 +2782,7 @@
       <c r="P6" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="61" t="n">
+      <c r="Q6" s="62" t="n">
         <v>2600</v>
       </c>
     </row>
@@ -2737,7 +2834,7 @@
       <c r="P7" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="61" t="n">
+      <c r="Q7" s="62" t="n">
         <v>2100</v>
       </c>
     </row>
@@ -2789,7 +2886,7 @@
       <c r="P8" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="61" t="n">
+      <c r="Q8" s="62" t="n">
         <v>2700</v>
       </c>
     </row>
@@ -2841,7 +2938,7 @@
       <c r="P9" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" s="61" t="n">
+      <c r="Q9" s="62" t="n">
         <v>4200</v>
       </c>
     </row>
@@ -2893,7 +2990,7 @@
       <c r="P10" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" s="61" t="n">
+      <c r="Q10" s="62" t="n">
         <v>4100</v>
       </c>
     </row>
@@ -2945,7 +3042,7 @@
       <c r="P11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="61" t="n">
+      <c r="Q11" s="62" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -2997,7 +3094,7 @@
       <c r="P12" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="61" t="n">
+      <c r="Q12" s="62" t="n">
         <v>3600</v>
       </c>
     </row>
@@ -3049,7 +3146,7 @@
       <c r="P13" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="61" t="n">
+      <c r="Q13" s="62" t="n">
         <v>2400</v>
       </c>
     </row>
@@ -3101,7 +3198,7 @@
       <c r="P14" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="61" t="n">
+      <c r="Q14" s="62" t="n">
         <v>2200</v>
       </c>
     </row>
@@ -3153,7 +3250,7 @@
       <c r="P15" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="61" t="n">
+      <c r="Q15" s="62" t="n">
         <v>3600</v>
       </c>
     </row>
@@ -3205,7 +3302,7 @@
       <c r="P16" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="61" t="n">
+      <c r="Q16" s="62" t="n">
         <v>5200</v>
       </c>
     </row>
@@ -3257,7 +3354,7 @@
       <c r="P17" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" s="61" t="n">
+      <c r="Q17" s="62" t="n">
         <v>6800</v>
       </c>
     </row>
@@ -3309,7 +3406,7 @@
       <c r="P18" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="61" t="n">
+      <c r="Q18" s="62" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -3361,7 +3458,7 @@
       <c r="P19" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="61" t="n">
+      <c r="Q19" s="62" t="n">
         <v>130</v>
       </c>
     </row>
@@ -3413,7 +3510,7 @@
       <c r="P20" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="61" t="n">
+      <c r="Q20" s="62" t="n">
         <v>140</v>
       </c>
     </row>
@@ -3465,7 +3562,7 @@
       <c r="P21" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="61" t="n">
+      <c r="Q21" s="62" t="n">
         <v>350</v>
       </c>
     </row>
@@ -3517,7 +3614,7 @@
       <c r="P22" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q22" s="61" t="n">
+      <c r="Q22" s="62" t="n">
         <v>9500</v>
       </c>
     </row>
@@ -3569,7 +3666,7 @@
       <c r="P23" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" s="61" t="n">
+      <c r="Q23" s="62" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -3621,7 +3718,7 @@
       <c r="P24" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" s="61" t="n">
+      <c r="Q24" s="62" t="n">
         <v>6500</v>
       </c>
     </row>
@@ -3673,7 +3770,7 @@
       <c r="P25" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" s="61" t="n">
+      <c r="Q25" s="62" t="n">
         <v>7500</v>
       </c>
     </row>
@@ -3725,7 +3822,7 @@
       <c r="P26" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="61" t="n">
+      <c r="Q26" s="62" t="n">
         <v>9000</v>
       </c>
     </row>
@@ -3777,7 +3874,7 @@
       <c r="P27" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" s="61" t="n">
+      <c r="Q27" s="62" t="n">
         <v>2200</v>
       </c>
     </row>
@@ -3829,12 +3926,12 @@
       <c r="P28" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" s="61" t="n">
+      <c r="Q28" s="62" t="n">
         <v>1800</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="62" t="inlineStr"/>
+      <c r="B29" s="63" t="inlineStr"/>
       <c r="C29" s="24" t="n">
         <v>0</v>
       </c>
@@ -3877,12 +3974,12 @@
       <c r="P29" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" s="61" t="n">
+      <c r="Q29" s="62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="62" t="inlineStr"/>
+      <c r="B30" s="63" t="inlineStr"/>
       <c r="C30" s="24" t="n">
         <v>0</v>
       </c>
@@ -3925,12 +4022,12 @@
       <c r="P30" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="61" t="n">
+      <c r="Q30" s="62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="62" t="inlineStr"/>
+      <c r="B31" s="63" t="inlineStr"/>
       <c r="C31" s="24" t="n">
         <v>0</v>
       </c>
@@ -3973,12 +4070,12 @@
       <c r="P31" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="61" t="n">
+      <c r="Q31" s="62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="62" t="inlineStr"/>
+      <c r="B32" s="63" t="inlineStr"/>
       <c r="C32" s="24" t="n">
         <v>0</v>
       </c>
@@ -4021,12 +4118,12 @@
       <c r="P32" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="61" t="n">
+      <c r="Q32" s="62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="62" t="inlineStr"/>
+      <c r="B33" s="63" t="inlineStr"/>
       <c r="C33" s="24" t="n">
         <v>0</v>
       </c>
@@ -4069,12 +4166,12 @@
       <c r="P33" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="61" t="n">
+      <c r="Q33" s="62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="62" t="inlineStr"/>
+      <c r="B34" s="63" t="inlineStr"/>
       <c r="C34" s="24" t="n">
         <v>0</v>
       </c>
@@ -4117,12 +4214,12 @@
       <c r="P34" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" s="61" t="n">
+      <c r="Q34" s="62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="62" t="inlineStr"/>
+      <c r="B35" s="63" t="inlineStr"/>
       <c r="C35" s="24" t="n">
         <v>0</v>
       </c>
@@ -4165,12 +4262,12 @@
       <c r="P35" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="61" t="n">
+      <c r="Q35" s="62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="62" t="inlineStr"/>
+      <c r="B36" s="63" t="inlineStr"/>
       <c r="C36" s="24" t="n">
         <v>0</v>
       </c>
@@ -4213,7 +4310,7 @@
       <c r="P36" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" s="61" t="n">
+      <c r="Q36" s="62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4252,7 +4349,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Metodologia de seleção: heurística de regras transparentes (não é um solver de otimização por programação linear) - prioriza menor número de produtos e aproveitamento cruzado de nutrientes (ex.: fonte de P que já traz enxofre evita precisar de sulfato de amônio). Todas as escolhas e doses são auditáveis nas fórmulas. Para otimização de custo mínimo real entre múltiplas fontes concorrentes, uma fase futura com Solver/VBA pode ser adicionada - ver Manual Técnico, seção Limitações.</t>
         </is>
@@ -4285,8 +4382,8 @@
           <t>N</t>
         </is>
       </c>
-      <c r="C9" s="44">
-        <f>IF('Dados de Entrada'!C8="Soja",Soja!C78,IF('Dados de Entrada'!C8="Milho",Milho!C80,'Outras Culturas'!D23))</f>
+      <c r="C9" s="45">
+        <f>IF('Dados de Entrada'!C8="Soja",Soja!C78,IF('Dados de Entrada'!C8="Milho",Milho!C80,'Outras Culturas'!D24))</f>
         <v/>
       </c>
     </row>
@@ -4296,8 +4393,8 @@
           <t>P2O5</t>
         </is>
       </c>
-      <c r="C10" s="44">
-        <f>IF('Dados de Entrada'!C8="Soja",Soja!C79,IF('Dados de Entrada'!C8="Milho",Milho!C81,'Outras Culturas'!D24))</f>
+      <c r="C10" s="45">
+        <f>IF('Dados de Entrada'!C8="Soja",Soja!C79,IF('Dados de Entrada'!C8="Milho",Milho!C81,'Outras Culturas'!D25))</f>
         <v/>
       </c>
     </row>
@@ -4307,8 +4404,8 @@
           <t>K2O</t>
         </is>
       </c>
-      <c r="C11" s="44">
-        <f>IF('Dados de Entrada'!C8="Soja",Soja!C80,IF('Dados de Entrada'!C8="Milho",Milho!C82,'Outras Culturas'!D25))</f>
+      <c r="C11" s="45">
+        <f>IF('Dados de Entrada'!C8="Soja",Soja!C80,IF('Dados de Entrada'!C8="Milho",Milho!C82,'Outras Culturas'!D26))</f>
         <v/>
       </c>
     </row>
@@ -4318,8 +4415,8 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C12" s="44">
-        <f>IF('Dados de Entrada'!C8="Soja",Soja!C81,IF('Dados de Entrada'!C8="Milho",Milho!C83,'Outras Culturas'!D26))</f>
+      <c r="C12" s="45">
+        <f>IF('Dados de Entrada'!C8="Soja",Soja!C81,IF('Dados de Entrada'!C8="Milho",Milho!C83,'Outras Culturas'!D27))</f>
         <v/>
       </c>
     </row>
@@ -4329,7 +4426,7 @@
           <t>Zn</t>
         </is>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="45">
         <f>IF('Dados de Entrada'!C8="Soja",Soja!C82,IF('Dados de Entrada'!C8="Milho",Milho!C84,0))</f>
         <v/>
       </c>
@@ -4340,7 +4437,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="45">
         <f>IF('Dados de Entrada'!C8="Soja",Soja!C83,IF('Dados de Entrada'!C8="Milho",Milho!C85,0))</f>
         <v/>
       </c>
@@ -4351,7 +4448,7 @@
           <t>Cu</t>
         </is>
       </c>
-      <c r="C15" s="44">
+      <c r="C15" s="45">
         <f>IF('Dados de Entrada'!C8="Soja",Soja!C84,IF('Dados de Entrada'!C8="Milho",Milho!C86,0))</f>
         <v/>
       </c>
@@ -4362,7 +4459,7 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="C16" s="44">
+      <c r="C16" s="45">
         <f>IF('Dados de Entrada'!C8="Soja",Soja!C85,IF('Dados de Entrada'!C8="Milho",Milho!C87,0))</f>
         <v/>
       </c>
@@ -4373,7 +4470,7 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="C17" s="44">
+      <c r="C17" s="45">
         <f>IF('Dados de Entrada'!C8="Soja",Soja!C86,IF('Dados de Entrada'!C8="Milho",Milho!C88,0))</f>
         <v/>
       </c>
@@ -4391,7 +4488,7 @@
           <t>Fonte de P2O5 escolhida</t>
         </is>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="32">
         <f>IF(C12&gt;0,"Superfosfato Simples","MAP (11-52-00)")</f>
         <v/>
       </c>
@@ -4402,7 +4499,7 @@
           <t>Fonte de K2O escolhida</t>
         </is>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <f>IF(Interpretação!E9="Baixo","K-Mag (Sulpomag)","Cloreto de Potássio")</f>
         <v/>
       </c>
@@ -4413,7 +4510,7 @@
           <t>Fonte de N escolhida</t>
         </is>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <f>IF(C20="Superfosfato Simples","Ureia",IF(C12&gt;0,"Sulfato de Amônio","Ureia"))</f>
         <v/>
       </c>
@@ -4424,7 +4521,7 @@
           <t>Fonte de micronutrientes escolhida</t>
         </is>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="32">
         <f>IF(OR(C13&gt;0,C14&gt;0,C15&gt;0,C16&gt;0,C17&gt;0),"FTE BR-12","-")</f>
         <v/>
       </c>
@@ -4469,7 +4566,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="31">
+      <c r="B27" s="32">
         <f>C22</f>
         <v/>
       </c>
@@ -4478,25 +4575,25 @@
           <t>N</t>
         </is>
       </c>
-      <c r="D27" s="58">
+      <c r="D27" s="59">
         <f>IF(B27="-",0,IFERROR(C9/(VLOOKUP(B27,TAB_FERT,2,FALSE)/100),0))</f>
         <v/>
       </c>
-      <c r="E27" s="52">
+      <c r="E27" s="53">
         <f>D27*'Dados de Entrada'!C7</f>
         <v/>
       </c>
-      <c r="F27" s="52">
+      <c r="F27" s="53">
         <f>IF(B27="-",0,IFERROR(VLOOKUP(B27,TAB_FERT,16,FALSE),0))</f>
         <v/>
       </c>
-      <c r="G27" s="63">
+      <c r="G27" s="64">
         <f>D27*F27/1000</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="31">
+      <c r="B28" s="32">
         <f>C20</f>
         <v/>
       </c>
@@ -4505,25 +4602,25 @@
           <t>P2O5</t>
         </is>
       </c>
-      <c r="D28" s="58">
+      <c r="D28" s="59">
         <f>IF(B28="-",0,IFERROR(C10/(VLOOKUP(B28,TAB_FERT,3,FALSE)/100),0))</f>
         <v/>
       </c>
-      <c r="E28" s="52">
+      <c r="E28" s="53">
         <f>D28*'Dados de Entrada'!C7</f>
         <v/>
       </c>
-      <c r="F28" s="52">
+      <c r="F28" s="53">
         <f>IF(B28="-",0,IFERROR(VLOOKUP(B28,TAB_FERT,16,FALSE),0))</f>
         <v/>
       </c>
-      <c r="G28" s="63">
+      <c r="G28" s="64">
         <f>D28*F28/1000</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="31">
+      <c r="B29" s="32">
         <f>C21</f>
         <v/>
       </c>
@@ -4532,25 +4629,25 @@
           <t>K2O</t>
         </is>
       </c>
-      <c r="D29" s="58">
+      <c r="D29" s="59">
         <f>IF(B29="-",0,IFERROR(C11/(VLOOKUP(B29,TAB_FERT,4,FALSE)/100),0))</f>
         <v/>
       </c>
-      <c r="E29" s="52">
+      <c r="E29" s="53">
         <f>D29*'Dados de Entrada'!C7</f>
         <v/>
       </c>
-      <c r="F29" s="52">
+      <c r="F29" s="53">
         <f>IF(B29="-",0,IFERROR(VLOOKUP(B29,TAB_FERT,16,FALSE),0))</f>
         <v/>
       </c>
-      <c r="G29" s="63">
+      <c r="G29" s="64">
         <f>D29*F29/1000</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="31">
+      <c r="B30" s="32">
         <f>C23</f>
         <v/>
       </c>
@@ -4559,19 +4656,19 @@
           <t>Zn/B/Cu/Mn/Mo (limitante)</t>
         </is>
       </c>
-      <c r="D30" s="58">
+      <c r="D30" s="59">
         <f>IF(B30="-",0,IFERROR(MAX(C13/9,C14/1.8,C15/0.8,C16/2,C17/0.1)*9/(VLOOKUP(B30,TAB_FERT,12,FALSE)/100),0))</f>
         <v/>
       </c>
-      <c r="E30" s="52">
+      <c r="E30" s="53">
         <f>D30*'Dados de Entrada'!C7</f>
         <v/>
       </c>
-      <c r="F30" s="52">
+      <c r="F30" s="53">
         <f>IF(B30="-",0,IFERROR(VLOOKUP(B30,TAB_FERT,16,FALSE),0))</f>
         <v/>
       </c>
-      <c r="G30" s="63">
+      <c r="G30" s="64">
         <f>D30*F30/1000</f>
         <v/>
       </c>
@@ -4589,7 +4686,7 @@
           <t>S necessário pela cultura (kg/ha)</t>
         </is>
       </c>
-      <c r="C33" s="49">
+      <c r="C33" s="50">
         <f>C12</f>
         <v/>
       </c>
@@ -4600,7 +4697,7 @@
           <t>S suprido pela fonte de N escolhida (kg/ha)</t>
         </is>
       </c>
-      <c r="C34" s="49">
+      <c r="C34" s="50">
         <f>D27*VLOOKUP(B27,TAB_FERT,5,FALSE)/100</f>
         <v/>
       </c>
@@ -4611,7 +4708,7 @@
           <t>S suprido pela fonte de P escolhida (kg/ha)</t>
         </is>
       </c>
-      <c r="C35" s="49">
+      <c r="C35" s="50">
         <f>D28*VLOOKUP(B28,TAB_FERT,5,FALSE)/100</f>
         <v/>
       </c>
@@ -4622,24 +4719,24 @@
           <t>S suprido pelo gesso agrícola recomendado (kg/ha)</t>
         </is>
       </c>
-      <c r="C36" s="37">
+      <c r="C36" s="38">
         <f>Gessagem!C22</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="41" t="inlineStr">
+      <c r="B37" s="42" t="inlineStr">
         <is>
           <t>Saldo de S (necessário - suprido)</t>
         </is>
       </c>
-      <c r="C37" s="58">
+      <c r="C37" s="59">
         <f>C12-C34-C35-C36</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="43" t="inlineStr">
+      <c r="B38" s="44" t="inlineStr">
         <is>
           <t>Se o saldo for positivo (faltando S), considere substituir a fonte de K por Sulfato de Potássio ou adicionar gesso/sulfato adicional.</t>
         </is>
@@ -4658,18 +4755,18 @@
           <t>Número de produtos utilizados</t>
         </is>
       </c>
-      <c r="C41" s="39">
+      <c r="C41" s="40">
         <f>SUMPRODUCT(--(D27:D30&gt;0))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="41" t="inlineStr">
+      <c r="B42" s="42" t="inlineStr">
         <is>
           <t>Custo total de fertilizantes (R$/ha)</t>
         </is>
       </c>
-      <c r="C42" s="64">
+      <c r="C42" s="65">
         <f>SUM(G27:G30)</f>
         <v/>
       </c>
@@ -4680,7 +4777,7 @@
           <t>Custo total de calcário (R$/ha)</t>
         </is>
       </c>
-      <c r="C43" s="63">
+      <c r="C43" s="64">
         <f>Calagem!C27*VLOOKUP("Calcário Dolomítico (PRNT 90%)",TAB_FERT,16,FALSE)</f>
         <v/>
       </c>
@@ -4691,29 +4788,29 @@
           <t>Custo total de gesso (R$/ha)</t>
         </is>
       </c>
-      <c r="C44" s="63">
+      <c r="C44" s="64">
         <f>Gessagem!C20/1000*VLOOKUP("Gesso Agrícola",TAB_FERT,16,FALSE)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="41" t="inlineStr">
+      <c r="B45" s="42" t="inlineStr">
         <is>
           <t>CUSTO TOTAL DE CORREÇÃO + ADUBAÇÃO (R$/ha)</t>
         </is>
       </c>
-      <c r="C45" s="64">
+      <c r="C45" s="65">
         <f>C42+C43+C44</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="41" t="inlineStr">
+      <c r="B46" s="42" t="inlineStr">
         <is>
           <t>CUSTO TOTAL PARA A ÁREA (R$)</t>
         </is>
       </c>
-      <c r="C46" s="64">
+      <c r="C46" s="65">
         <f>C45*'Dados de Entrada'!C7</f>
         <v/>
       </c>
@@ -4772,7 +4869,7 @@
           <t>Fazenda/Talhão</t>
         </is>
       </c>
-      <c r="C4" s="38">
+      <c r="C4" s="39">
         <f>'Dados de Entrada'!C4</f>
         <v/>
       </c>
@@ -4783,7 +4880,7 @@
           <t>Município/UF</t>
         </is>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="39">
         <f>'Dados de Entrada'!C5</f>
         <v/>
       </c>
@@ -4794,7 +4891,7 @@
           <t>Cultura</t>
         </is>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="39">
         <f>'Dados de Entrada'!C8</f>
         <v/>
       </c>
@@ -4805,7 +4902,7 @@
           <t>Área (ha)</t>
         </is>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="56">
         <f>'Dados de Entrada'!C7</f>
         <v/>
       </c>
@@ -4816,7 +4913,7 @@
           <t>Produtividade meta</t>
         </is>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="38">
         <f>'Dados de Entrada'!C9</f>
         <v/>
       </c>
@@ -4834,7 +4931,7 @@
           <t>Limitações identificadas (Muito baixo/Baixo, ou m% Alto)</t>
         </is>
       </c>
-      <c r="C11" s="65">
+      <c r="C11" s="66">
         <f>Interpretação!B22</f>
         <v/>
       </c>
@@ -4852,7 +4949,7 @@
           <t>Método de calagem recomendado</t>
         </is>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="39">
         <f>Calagem!C26</f>
         <v/>
       </c>
@@ -4863,7 +4960,7 @@
           <t>Calcário - dose final (t/ha)</t>
         </is>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="33">
         <f>Calagem!C27</f>
         <v/>
       </c>
@@ -4874,7 +4971,7 @@
           <t>Calcário - total área (t)</t>
         </is>
       </c>
-      <c r="C17" s="66">
+      <c r="C17" s="67">
         <f>Calagem!C28</f>
         <v/>
       </c>
@@ -4885,7 +4982,7 @@
           <t>Gesso - recomendado?</t>
         </is>
       </c>
-      <c r="C18" s="38">
+      <c r="C18" s="39">
         <f>Gessagem!C15</f>
         <v/>
       </c>
@@ -4896,7 +4993,7 @@
           <t>Gesso - dose (kg/ha)</t>
         </is>
       </c>
-      <c r="C19" s="67">
+      <c r="C19" s="68">
         <f>Gessagem!C20</f>
         <v/>
       </c>
@@ -4936,16 +5033,16 @@
           <t>N</t>
         </is>
       </c>
-      <c r="C23" s="44">
+      <c r="C23" s="45">
         <f>'Mistura de Fertilizantes'!C9</f>
         <v/>
       </c>
-      <c r="D23" s="31" t="inlineStr">
+      <c r="D23" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E23" s="39" t="inlineStr"/>
+      <c r="E23" s="40" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="8" t="inlineStr">
@@ -4953,15 +5050,15 @@
           <t>P2O5</t>
         </is>
       </c>
-      <c r="C24" s="44">
+      <c r="C24" s="45">
         <f>'Mistura de Fertilizantes'!C10</f>
         <v/>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <f>Interpretação!E6</f>
         <v/>
       </c>
-      <c r="E24" s="39">
+      <c r="E24" s="40">
         <f>IF(D24="Muito baixo",1,IF(D24="Baixo",2,IF(D24="Médio",3,IF(D24="Adequado",4,IF(D24="Alto",5,IF(D24="Muito alto",6,""))))))</f>
         <v/>
       </c>
@@ -4972,15 +5069,15 @@
           <t>K2O</t>
         </is>
       </c>
-      <c r="C25" s="44">
+      <c r="C25" s="45">
         <f>'Mistura de Fertilizantes'!C11</f>
         <v/>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <f>Interpretação!E7</f>
         <v/>
       </c>
-      <c r="E25" s="39">
+      <c r="E25" s="40">
         <f>IF(D25="Muito baixo",1,IF(D25="Baixo",2,IF(D25="Médio",3,IF(D25="Adequado",4,IF(D25="Alto",5,IF(D25="Muito alto",6,""))))))</f>
         <v/>
       </c>
@@ -4991,15 +5088,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C26" s="44">
+      <c r="C26" s="45">
         <f>'Mistura de Fertilizantes'!C12</f>
         <v/>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="32">
         <f>Interpretação!E12</f>
         <v/>
       </c>
-      <c r="E26" s="39">
+      <c r="E26" s="40">
         <f>IF(D26="Muito baixo",1,IF(D26="Baixo",2,IF(D26="Médio",3,IF(D26="Adequado",4,IF(D26="Alto",5,IF(D26="Muito alto",6,""))))))</f>
         <v/>
       </c>
@@ -5010,15 +5107,15 @@
           <t>Zn</t>
         </is>
       </c>
-      <c r="C27" s="44">
+      <c r="C27" s="45">
         <f>'Mistura de Fertilizantes'!C13</f>
         <v/>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="32">
         <f>Interpretação!E13</f>
         <v/>
       </c>
-      <c r="E27" s="39">
+      <c r="E27" s="40">
         <f>IF(D27="Muito baixo",1,IF(D27="Baixo",2,IF(D27="Médio",3,IF(D27="Adequado",4,IF(D27="Alto",5,IF(D27="Muito alto",6,""))))))</f>
         <v/>
       </c>
@@ -5029,15 +5126,15 @@
           <t>B</t>
         </is>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="45">
         <f>'Mistura de Fertilizantes'!C14</f>
         <v/>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <f>Interpretação!E17</f>
         <v/>
       </c>
-      <c r="E28" s="39">
+      <c r="E28" s="40">
         <f>IF(D28="Muito baixo",1,IF(D28="Baixo",2,IF(D28="Médio",3,IF(D28="Adequado",4,IF(D28="Alto",5,IF(D28="Muito alto",6,""))))))</f>
         <v/>
       </c>
@@ -5048,15 +5145,15 @@
           <t>Cu</t>
         </is>
       </c>
-      <c r="C29" s="44">
+      <c r="C29" s="45">
         <f>'Mistura de Fertilizantes'!C15</f>
         <v/>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="32">
         <f>Interpretação!E14</f>
         <v/>
       </c>
-      <c r="E29" s="39">
+      <c r="E29" s="40">
         <f>IF(D29="Muito baixo",1,IF(D29="Baixo",2,IF(D29="Médio",3,IF(D29="Adequado",4,IF(D29="Alto",5,IF(D29="Muito alto",6,""))))))</f>
         <v/>
       </c>
@@ -5067,15 +5164,15 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="C30" s="44">
+      <c r="C30" s="45">
         <f>'Mistura de Fertilizantes'!C16</f>
         <v/>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="32">
         <f>Interpretação!E15</f>
         <v/>
       </c>
-      <c r="E30" s="39">
+      <c r="E30" s="40">
         <f>IF(D30="Muito baixo",1,IF(D30="Baixo",2,IF(D30="Médio",3,IF(D30="Adequado",4,IF(D30="Alto",5,IF(D30="Muito alto",6,""))))))</f>
         <v/>
       </c>
@@ -5086,15 +5183,15 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="C31" s="44">
+      <c r="C31" s="45">
         <f>'Mistura de Fertilizantes'!C17</f>
         <v/>
       </c>
-      <c r="D31" s="31">
+      <c r="D31" s="32">
         <f>Interpretação!E18</f>
         <v/>
       </c>
-      <c r="E31" s="39">
+      <c r="E31" s="40">
         <f>IF(D31="Muito baixo",1,IF(D31="Baixo",2,IF(D31="Médio",3,IF(D31="Adequado",4,IF(D31="Alto",5,IF(D31="Muito alto",6,""))))))</f>
         <v/>
       </c>
@@ -5112,7 +5209,7 @@
           <t>Custo de correção + adubação (R$/ha)</t>
         </is>
       </c>
-      <c r="C34" s="55">
+      <c r="C34" s="56">
         <f>'Mistura de Fertilizantes'!C45</f>
         <v/>
       </c>
@@ -5123,7 +5220,7 @@
           <t>Custo total para a área (R$)</t>
         </is>
       </c>
-      <c r="C35" s="55">
+      <c r="C35" s="56">
         <f>'Mistura de Fertilizantes'!C46</f>
         <v/>
       </c>
@@ -5593,7 +5690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G46"/>
+  <dimension ref="B1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6358,15 +6455,67 @@
         <v/>
       </c>
     </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>5. Premissas de Manejo e Cálculo (únicas - as culturas apenas leem estes valores)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>Inoculação com Bradyrhizobium realizada corretamente? (Soja)</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>Cultura anterior foi leguminosa? (crédito de N - Milho/cereais)</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>Eficiência de aproveitamento do N (%) - padrão</t>
+        </is>
+      </c>
+      <c r="C51" s="30" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>Eficiência de aproveitamento do S (%) - padrão</t>
+        </is>
+      </c>
+      <c r="C52" s="30" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B16:G16"/>
     <mergeCell ref="B22:G22"/>
     <mergeCell ref="B41:G41"/>
     <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B48:G48"/>
   </mergeCells>
-  <dataValidations count="34">
+  <dataValidations count="36">
     <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Selecione" prompt="Selecione a UF" type="list">
       <formula1>"AC,AL,AP,AM,BA,CE,DF,ES,GO,MA,MT,MS,MG,PA,PB,PR,PE,PI,RJ,RN,RS,RO,RR,SC,SP,SE,TO"</formula1>
     </dataValidation>
@@ -6405,6 +6554,12 @@
     </dataValidation>
     <dataValidation sqref="D31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"mmolc/dm³,cmolc/dm³"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sim,Não"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sim,Não"</formula1>
     </dataValidation>
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor impossível" error="A área deve ser maior que zero." type="decimal" operator="greaterThanOrEqual">
       <formula1>0.01</formula1>
@@ -6503,7 +6658,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Estas tabelas alimentam a aba "Interpretação" por busca aproximada (limite inferior de cada classe). Podem ser editadas para refletir um boletim regional mais atualizado — a planilha recalcula automaticamente. Fonte e nível de confiança de cada bloco estão registrados ao lado.</t>
         </is>
@@ -6515,7 +6670,7 @@
           <t>Fósforo (mg/dm³) — Sistema Cerrado, Sequeiro</t>
         </is>
       </c>
-      <c r="E5" s="30" t="inlineStr">
+      <c r="E5" s="31" t="inlineStr">
         <is>
           <t>Fonte: Sousa, D.M.G.; Lobato, E. Cerrado: Correção do Solo e Adubação. Embrapa Cerrados, 2004.  |  Confiança: Alta</t>
         </is>
@@ -6534,50 +6689,50 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="B7" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>Muito baixo</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="31" t="n">
+      <c r="B9" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Adequado</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
@@ -6589,7 +6744,7 @@
           <t>Fósforo (mg/dm³) — Sistema Cerrado, Irrigado</t>
         </is>
       </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t>Fonte: Sousa, D.M.G.; Lobato, E. Cerrado: Correção do Solo e Adubação. Embrapa Cerrados, 2004.  |  Confiança: Alta</t>
         </is>
@@ -6608,50 +6763,50 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="B15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>Muito baixo</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="31" t="n">
+      <c r="B16" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="C16" s="31" t="inlineStr">
+      <c r="C16" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="31" t="n">
+      <c r="B17" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C17" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="31" t="n">
+      <c r="B18" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="C18" s="31" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
         <is>
           <t>Adequado</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="31" t="n">
+      <c r="B19" s="32" t="n">
         <v>35</v>
       </c>
-      <c r="C19" s="31" t="inlineStr">
+      <c r="C19" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
@@ -6663,7 +6818,7 @@
           <t>Potássio trocável (mmolc/dm³)</t>
         </is>
       </c>
-      <c r="E21" s="30" t="inlineStr">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>Fonte: Raij et al., Boletim Técnico 100, IAC.  |  Confiança: Alta (faixas) / Média (sem estratificação por CTC do original)</t>
         </is>
@@ -6682,50 +6837,50 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="31" t="inlineStr">
+      <c r="B23" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
         <is>
           <t>Muito baixo</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="31" t="n">
+      <c r="B24" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="C24" s="31" t="inlineStr">
+      <c r="C24" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="32" t="n">
         <v>1.5</v>
       </c>
-      <c r="C25" s="31" t="inlineStr">
+      <c r="C25" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="31" t="n">
+      <c r="B26" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="31" t="inlineStr">
+      <c r="C26" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="31" t="n">
+      <c r="B27" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="C27" s="31" t="inlineStr">
+      <c r="C27" s="32" t="inlineStr">
         <is>
           <t>Muito alto</t>
         </is>
@@ -6737,7 +6892,7 @@
           <t>Matéria Orgânica (g/dm³)</t>
         </is>
       </c>
-      <c r="E29" s="30" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>Fonte: Síntese didática consolidada na literatura agronômica brasileira (não reverificada diretamente contra o Boletim 100 nesta versão).  |  Confiança: Média</t>
         </is>
@@ -6756,30 +6911,30 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="31" t="inlineStr">
+      <c r="B31" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="31" t="n">
+      <c r="B32" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="C32" s="31" t="inlineStr">
+      <c r="C32" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="31" t="n">
+      <c r="B33" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="C33" s="31" t="inlineStr">
+      <c r="C33" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
@@ -6791,7 +6946,7 @@
           <t>Cálcio trocável (mmolc/dm³)</t>
         </is>
       </c>
-      <c r="E35" s="30" t="inlineStr">
+      <c r="E35" s="31" t="inlineStr">
         <is>
           <t>Fonte: Faixas de referência de uso corrente na literatura agronômica brasileira para cálcio trocável (não reverificadas diretamente contra o Boletim 100 nesta versão).  |  Confiança: Baixa-Média</t>
         </is>
@@ -6810,30 +6965,30 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="31" t="inlineStr">
+      <c r="B37" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="31" t="n">
+      <c r="B38" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="31" t="inlineStr">
+      <c r="C38" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="31" t="n">
+      <c r="B39" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="C39" s="31" t="inlineStr">
+      <c r="C39" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
@@ -6845,7 +7000,7 @@
           <t>Magnésio trocável (mmolc/dm³)</t>
         </is>
       </c>
-      <c r="E41" s="30" t="inlineStr">
+      <c r="E41" s="31" t="inlineStr">
         <is>
           <t>Fonte: Faixas de referência de uso corrente na literatura agronômica brasileira para magnésio trocável (não reverificadas diretamente contra o Boletim 100 nesta versão).  |  Confiança: Baixa-Média</t>
         </is>
@@ -6864,30 +7019,30 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="31" t="inlineStr">
+      <c r="B43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="31" t="n">
+      <c r="B44" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="C44" s="31" t="inlineStr">
+      <c r="C44" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="31" t="n">
+      <c r="B45" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="C45" s="31" t="inlineStr">
+      <c r="C45" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
@@ -6899,7 +7054,7 @@
           <t>pH (CaCl₂)</t>
         </is>
       </c>
-      <c r="E47" s="30" t="inlineStr">
+      <c r="E47" s="31" t="inlineStr">
         <is>
           <t>Fonte: Faixa de referência de uso amplo na prática agronômica brasileira (pH em CaCl₂); o alvo técnico de correção é definido pelo V% e não pelo pH isolado.  |  Confiança: Média</t>
         </is>
@@ -6918,50 +7073,50 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="31" t="inlineStr">
+      <c r="B49" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="32" t="inlineStr">
         <is>
           <t>Muito baixo</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="31" t="n">
+      <c r="B50" s="32" t="n">
         <v>4.3</v>
       </c>
-      <c r="C50" s="31" t="inlineStr">
+      <c r="C50" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="31" t="n">
+      <c r="B51" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="C51" s="31" t="inlineStr">
+      <c r="C51" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="31" t="n">
+      <c r="B52" s="32" t="n">
         <v>5.5</v>
       </c>
-      <c r="C52" s="31" t="inlineStr">
+      <c r="C52" s="32" t="inlineStr">
         <is>
           <t>Bom</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="31" t="n">
+      <c r="B53" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="C53" s="31" t="inlineStr">
+      <c r="C53" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
@@ -6973,7 +7128,7 @@
           <t>Saturação por Bases — V%</t>
         </is>
       </c>
-      <c r="E55" s="30" t="inlineStr">
+      <c r="E55" s="31" t="inlineStr">
         <is>
           <t>Fonte: Referência consolidada na literatura agronômica brasileira (Raij et al., Boletim 100 - faixas gerais).  |  Confiança: Média</t>
         </is>
@@ -6992,50 +7147,50 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" s="31" t="inlineStr">
+      <c r="B57" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="32" t="inlineStr">
         <is>
           <t>Muito baixo</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="31" t="n">
+      <c r="B58" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="C58" s="31" t="inlineStr">
+      <c r="C58" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="31" t="n">
+      <c r="B59" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="C59" s="31" t="inlineStr">
+      <c r="C59" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="31" t="n">
+      <c r="B60" s="32" t="n">
         <v>70</v>
       </c>
-      <c r="C60" s="31" t="inlineStr">
+      <c r="C60" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="31" t="n">
+      <c r="B61" s="32" t="n">
         <v>90</v>
       </c>
-      <c r="C61" s="31" t="inlineStr">
+      <c r="C61" s="32" t="inlineStr">
         <is>
           <t>Muito alto</t>
         </is>
@@ -7047,7 +7202,7 @@
           <t>Saturação por Alumínio — m%</t>
         </is>
       </c>
-      <c r="E63" s="30" t="inlineStr">
+      <c r="E63" s="31" t="inlineStr">
         <is>
           <t>Fonte: Sousa &amp; Lobato (2004) - limiar de 20% usado como critério de gessagem; faixas completas de referência didática.  |  Confiança: Média-Alta</t>
         </is>
@@ -7066,40 +7221,40 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C65" s="31" t="inlineStr">
+      <c r="B65" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="31" t="n">
+      <c r="B66" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="C66" s="31" t="inlineStr">
+      <c r="C66" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="31" t="n">
+      <c r="B67" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="C67" s="31" t="inlineStr">
+      <c r="C67" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="31" t="n">
+      <c r="B68" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="C68" s="31" t="inlineStr">
+      <c r="C68" s="32" t="inlineStr">
         <is>
           <t>Muito alto</t>
         </is>
@@ -7111,7 +7266,7 @@
           <t>Micronutriente — Zn (mg/dm³)</t>
         </is>
       </c>
-      <c r="E70" s="30" t="inlineStr">
+      <c r="E70" s="31" t="inlineStr">
         <is>
           <t>Fonte: Valores de referência de uso corrente na prática agronômica brasileira; tabelas completas do Boletim 100 e CQFS-RS/SC não confirmadas nesta versão.  |  Confiança: Baixa-Média</t>
         </is>
@@ -7130,30 +7285,30 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" s="31" t="inlineStr">
+      <c r="B72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="31" t="n">
+      <c r="B73" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="C73" s="31" t="inlineStr">
+      <c r="C73" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="31" t="n">
+      <c r="B74" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="C74" s="31" t="inlineStr">
+      <c r="C74" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
@@ -7165,7 +7320,7 @@
           <t>Micronutriente — Cu (mg/dm³)</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E76" s="31" t="inlineStr">
         <is>
           <t>Fonte: Valores de referência de uso corrente na prática agronômica brasileira; tabelas completas do Boletim 100 e CQFS-RS/SC não confirmadas nesta versão.  |  Confiança: Baixa-Média</t>
         </is>
@@ -7184,30 +7339,30 @@
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" s="31" t="inlineStr">
+      <c r="B78" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="31" t="n">
+      <c r="B79" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="C79" s="31" t="inlineStr">
+      <c r="C79" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="31" t="n">
+      <c r="B80" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="C80" s="31" t="inlineStr">
+      <c r="C80" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
@@ -7219,7 +7374,7 @@
           <t>Micronutriente — Mn (mg/dm³)</t>
         </is>
       </c>
-      <c r="E82" s="30" t="inlineStr">
+      <c r="E82" s="31" t="inlineStr">
         <is>
           <t>Fonte: Valores de referência de uso corrente na prática agronômica brasileira; tabelas completas do Boletim 100 e CQFS-RS/SC não confirmadas nesta versão.  |  Confiança: Baixa-Média</t>
         </is>
@@ -7238,30 +7393,30 @@
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="31" t="inlineStr">
+      <c r="B84" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="31" t="n">
+      <c r="B85" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="C85" s="31" t="inlineStr">
+      <c r="C85" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="31" t="n">
+      <c r="B86" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="C86" s="31" t="inlineStr">
+      <c r="C86" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
@@ -7273,7 +7428,7 @@
           <t>Micronutriente — Fe (mg/dm³)</t>
         </is>
       </c>
-      <c r="E88" s="30" t="inlineStr">
+      <c r="E88" s="31" t="inlineStr">
         <is>
           <t>Fonte: Valores de referência de uso corrente na prática agronômica brasileira; tabelas completas do Boletim 100 e CQFS-RS/SC não confirmadas nesta versão.  |  Confiança: Baixa-Média</t>
         </is>
@@ -7292,30 +7447,30 @@
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" s="31" t="inlineStr">
+      <c r="B90" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="31" t="n">
+      <c r="B91" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="C91" s="31" t="inlineStr">
+      <c r="C91" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="31" t="n">
+      <c r="B92" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="C92" s="31" t="inlineStr">
+      <c r="C92" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
@@ -7327,7 +7482,7 @@
           <t>Micronutriente — B (mg/dm³)</t>
         </is>
       </c>
-      <c r="E94" s="30" t="inlineStr">
+      <c r="E94" s="31" t="inlineStr">
         <is>
           <t>Fonte: Valores de referência de uso corrente na prática agronômica brasileira; tabelas completas do Boletim 100 e CQFS-RS/SC não confirmadas nesta versão.  |  Confiança: Baixa-Média</t>
         </is>
@@ -7346,30 +7501,30 @@
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C96" s="31" t="inlineStr">
+      <c r="B96" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="31" t="n">
+      <c r="B97" s="32" t="n">
         <v>0.21</v>
       </c>
-      <c r="C97" s="31" t="inlineStr">
+      <c r="C97" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="31" t="n">
+      <c r="B98" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="C98" s="31" t="inlineStr">
+      <c r="C98" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
@@ -7381,7 +7536,7 @@
           <t>Micronutriente — Mo (mg/dm³)</t>
         </is>
       </c>
-      <c r="E100" s="30" t="inlineStr">
+      <c r="E100" s="31" t="inlineStr">
         <is>
           <t>Fonte: Valores de referência de uso corrente na prática agronômica brasileira; tabelas completas do Boletim 100 e CQFS-RS/SC não confirmadas nesta versão.  |  Confiança: Baixa-Média</t>
         </is>
@@ -7400,30 +7555,30 @@
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" s="31" t="inlineStr">
+      <c r="B102" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="32" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="31" t="n">
+      <c r="B103" s="32" t="n">
         <v>0.05</v>
       </c>
-      <c r="C103" s="31" t="inlineStr">
+      <c r="C103" s="32" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="31" t="n">
+      <c r="B104" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="C104" s="31" t="inlineStr">
+      <c r="C104" s="32" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
@@ -7512,7 +7667,7 @@
           <t>pH (CaCl₂)</t>
         </is>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="33">
         <f>'Dados de Entrada'!E24</f>
         <v/>
       </c>
@@ -7521,11 +7676,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="34">
         <f>VLOOKUP(C4,TAB_PH,2,TRUE)</f>
         <v/>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="35">
         <f>IF(OR(E4="Muito baixo",E4="Baixo"),"Prioridade de correção/construção de fertilidade",IF(E4="Médio","Adequado - manter e monitorar",IF(OR(E4="Alto",E4="Muito alto"),"Sem prioridade - risco de excesso/custo desnecessário se adubar",IF(E4="Adequado","Adequado - manter e monitorar","-"))))</f>
         <v/>
       </c>
@@ -7536,7 +7691,7 @@
           <t>Matéria Orgânica</t>
         </is>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="33">
         <f>'Dados de Entrada'!E25</f>
         <v/>
       </c>
@@ -7545,11 +7700,11 @@
           <t>g/dm³</t>
         </is>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="34">
         <f>VLOOKUP(C5,TAB_MO,2,TRUE)</f>
         <v/>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="35">
         <f>IF(OR(E5="Muito baixo",E5="Baixo"),"Prioridade de correção/construção de fertilidade",IF(E5="Médio","Adequado - manter e monitorar",IF(OR(E5="Alto",E5="Muito alto"),"Sem prioridade - risco de excesso/custo desnecessário se adubar",IF(E5="Adequado","Adequado - manter e monitorar","-"))))</f>
         <v/>
       </c>
@@ -7560,7 +7715,7 @@
           <t>Fósforo (P)</t>
         </is>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="33">
         <f>'Dados de Entrada'!E26</f>
         <v/>
       </c>
@@ -7569,11 +7724,11 @@
           <t>mg/dm³</t>
         </is>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="34">
         <f>VLOOKUP(C6,IF('Dados de Entrada'!C11="Irrigado",TAB_P_IRR,TAB_P_SEQ),2,TRUE)</f>
         <v/>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="35">
         <f>IF(OR(E6="Muito baixo",E6="Baixo"),"Prioridade de correção/construção de fertilidade",IF(E6="Médio","Adequado - manter e monitorar",IF(OR(E6="Alto",E6="Muito alto"),"Sem prioridade - risco de excesso/custo desnecessário se adubar",IF(E6="Adequado","Adequado - manter e monitorar","-"))))</f>
         <v/>
       </c>
@@ -7584,7 +7739,7 @@
           <t>Potássio (K)</t>
         </is>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="33">
         <f>'Dados de Entrada'!E27</f>
         <v/>
       </c>
@@ -7593,11 +7748,11 @@
           <t>mmolc/dm³</t>
         </is>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="34">
         <f>VLOOKUP(C7,TAB_K,2,TRUE)</f>
         <v/>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="35">
         <f>IF(OR(E7="Muito baixo",E7="Baixo"),"Prioridade de correção/construção de fertilidade",IF(E7="Médio","Adequado - manter e monitorar",IF(OR(E7="Alto",E7="Muito alto"),"Sem prioridade - risco de excesso/custo desnecessário se adubar",IF(E7="Adequado","Adequado - manter e monitorar","-"))))</f>
         <v/>
       </c>
@@ -7608,7 +7763,7 @@
           <t>Cálcio (Ca)</t>
         </is>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <f>'Dados de Entrada'!E28</f>
         <v/>
       </c>
@@ -7617,11 +7772,11 @@
           <t>mmolc/dm³</t>
         </is>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <f>VLOOKUP(C8,TAB_CA,2,TRUE)</f>
         <v/>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="35">
         <f>IF(OR(E8="Muito baixo",E8="Baixo"),"Prioridade de correção/construção de fertilidade",IF(E8="Médio","Adequado - manter e monitorar",IF(OR(E8="Alto",E8="Muito alto"),"Sem prioridade - risco de excesso/custo desnecessário se adubar",IF(E8="Adequado","Adequado - manter e monitorar","-"))))</f>
         <v/>
       </c>
@@ -7632,7 +7787,7 @@
           <t>Magnésio (Mg)</t>
         </is>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <f>'Dados de Entrada'!E29</f>
         <v/>
       </c>
@@ -7641,11 +7796,11 @@
           <t>mmolc/dm³</t>
         </is>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="34">
         <f>VLOOKUP(C9,TAB_MG,2,TRUE)</f>
         <v/>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="35">
         <f>IF(OR(E9="Muito baixo",E9="Baixo"),"Prioridade de correção/construção de fertilidade",IF(E9="Médio","Adequado - manter e monitorar",IF(OR(E9="Alto",E9="Muito alto"),"Sem prioridade - risco de excesso/custo desnecessário se adubar",IF(E9="Adequado","Adequado - manter e monitorar","-"))))</f>
         <v/>
       </c>
@@ -7656,7 +7811,7 @@
           <t>Saturação por Bases (V%)</t>
         </is>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="33">
         <f>'Dados de Entrada'!C45</f>
         <v/>
       </c>
@@ -7665,11 +7820,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="34">
         <f>VLOOKUP(C10,TAB_V,2,TRUE)</f>
         <v/>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="35">
         <f>IF(OR(E10="Muito baixo",E10="Baixo"),"Prioridade de correção/construção de fertilidade",IF(E10="Médio","Adequado - manter e monitorar",IF(OR(E10="Alto",E10="Muito alto"),"Sem prioridade - risco de excesso/custo desnecessário se adubar",IF(E10="Adequado","Adequado - manter e monitorar","-"))))</f>
         <v/>
       </c>
@@ -7680,7 +7835,7 @@
           <t>Saturação por Alumínio (m%)</t>
         </is>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>'Dados de Entrada'!C46</f>
         <v/>
       </c>
@@ -7689,11 +7844,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="34">
         <f>VLOOKUP(C11,TAB_M,2,TRUE)</f>
         <v/>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="35">
         <f>IF(OR(E11="Alto",E11="Muito alto"),"Prioridade de correção (calagem/gessagem)",IF(E11="Médio","Atenção - monitorar risco de toxidez",IF(OR(E11="Baixo",E11="Muito baixo"),"Sem restrição - condição favorável","-")))</f>
         <v/>
       </c>
@@ -7704,7 +7859,7 @@
           <t>Enxofre (S-SO₄)</t>
         </is>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>'Dados de Entrada'!E32</f>
         <v/>
       </c>
@@ -7713,11 +7868,11 @@
           <t>mg/dm³</t>
         </is>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="34">
         <f>IF(C12&lt;5,"Baixo",IF(C12&lt;=10,"Médio","Alto"))</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>IF(OR(E12="Muito baixo",E12="Baixo"),"Prioridade de correção/construção de fertilidade",IF(E12="Médio","Adequado - manter e monitorar",IF(OR(E12="Alto",E12="Muito alto"),"Sem prioridade - risco de excesso/custo desnecessário se adubar",IF(E12="Adequado","Adequado - manter e monitorar","-"))))</f>
         <v/>
       </c>
@@ -7728,7 +7883,7 @@
           <t>Zinco (Zn)</t>
         </is>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <f>'Dados de Entrada'!E37</f>
         <v/>
       </c>
@@ -7737,11 +7892,11 @@
           <t>mg/dm³</t>
         </is>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="34">
         <f>VLOOKUP(C13,TAB_ZN,2,TRUE)</f>
         <v/>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="35">
         <f>IF(OR(E13="Muito baixo",E13="Baixo"),"Prioridade de correção/construção de fertilidade",IF(E13="Médio","Adequado - manter e monitorar",IF(OR(E13="Alto",E13="Muito alto"),"Sem prioridade - risco de excesso/custo desnecessário se adubar",IF(E13="Adequado","Adequado - manter e monitorar","-"))))</f>
         <v/>
       </c>
@@ -7752,7 +7907,7 @@
           <t>Cobre (Cu)</t>
         </is>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>'Dados de Entrada'!E34</f>
         <v/>
       </c>
@@ -7761,11 +7916,11 @@
           <t>mg/dm³</t>
         </is>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="34">
         <f>VLOOKUP(C14,TAB_CU,2,TRUE)</f>
         <v/>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="35">
         <f>IF(OR(E14="Muito baixo",E14="Baixo"),"Prioridade de correção/construção de fertilidade",IF(E14="Médio","Adequado - manter e monitorar",IF(OR(E14="Alto",E14="Muito alto"),"Sem prioridade - risco de excesso/custo desnecessário se adubar",IF(E14="Adequado","Adequado - manter e monitorar","-"))))</f>
         <v/>
       </c>
@@ -7776,7 +7931,7 @@
           <t>Manganês (Mn)</t>
         </is>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="33">
         <f>'Dados de Entrada'!E36</f>
         <v/>
       </c>
@@ -7785,11 +7940,11 @@
           <t>mg/dm³</t>
         </is>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="34">
         <f>VLOOKUP(C15,TAB_MN,2,TRUE)</f>
         <v/>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="35">
         <f>IF(OR(E15="Muito baixo",E15="Baixo"),"Prioridade de correção/construção de fertilidade",IF(E15="Médio","Adequado - manter e monitorar",IF(OR(E15="Alto",E15="Muito alto"),"Sem prioridade - risco de excesso/custo desnecessário se adubar",IF(E15="Adequado","Adequado - manter e monitorar","-"))))</f>
         <v/>
       </c>
@@ -7800,7 +7955,7 @@
           <t>Ferro (Fe)</t>
         </is>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="33">
         <f>'Dados de Entrada'!E35</f>
         <v/>
       </c>
@@ -7809,11 +7964,11 @@
           <t>mg/dm³</t>
         </is>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="34">
         <f>VLOOKUP(C16,TAB_FE,2,TRUE)</f>
         <v/>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="35">
         <f>IF(OR(E16="Muito baixo",E16="Baixo"),"Prioridade de correção/construção de fertilidade",IF(E16="Médio","Adequado - manter e monitorar",IF(OR(E16="Alto",E16="Muito alto"),"Sem prioridade - risco de excesso/custo desnecessário se adubar",IF(E16="Adequado","Adequado - manter e monitorar","-"))))</f>
         <v/>
       </c>
@@ -7824,7 +7979,7 @@
           <t>Boro (B)</t>
         </is>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="33">
         <f>'Dados de Entrada'!E33</f>
         <v/>
       </c>
@@ -7833,11 +7988,11 @@
           <t>mg/dm³</t>
         </is>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="34">
         <f>VLOOKUP(C17,TAB_B,2,TRUE)</f>
         <v/>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="35">
         <f>IF(OR(E17="Muito baixo",E17="Baixo"),"Prioridade de correção/construção de fertilidade",IF(E17="Médio","Adequado - manter e monitorar",IF(OR(E17="Alto",E17="Muito alto"),"Sem prioridade - risco de excesso/custo desnecessário se adubar",IF(E17="Adequado","Adequado - manter e monitorar","-"))))</f>
         <v/>
       </c>
@@ -7848,7 +8003,7 @@
           <t>Molibdênio (Mo)</t>
         </is>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="33">
         <f>'Dados de Entrada'!E38</f>
         <v/>
       </c>
@@ -7857,11 +8012,11 @@
           <t>mg/dm³</t>
         </is>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="34">
         <f>VLOOKUP(C18,TAB_MOL,2,TRUE)</f>
         <v/>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="35">
         <f>IF(OR(E18="Muito baixo",E18="Baixo"),"Prioridade de correção/construção de fertilidade",IF(E18="Médio","Adequado - manter e monitorar",IF(OR(E18="Alto",E18="Muito alto"),"Sem prioridade - risco de excesso/custo desnecessário se adubar",IF(E18="Adequado","Adequado - manter e monitorar","-"))))</f>
         <v/>
       </c>
@@ -7881,95 +8036,95 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="B22" s="35">
+      <c r="B22" s="36">
         <f>IF(COUNTIF(H22:H36,"?*")=0,"Nenhuma limitação identificada - solo em nível adequado a alto nos parâmetros avaliados",_xlfn.TEXTJOIN(", ",TRUE,H22:H36))</f>
         <v/>
       </c>
-      <c r="H22" s="36">
+      <c r="H22" s="37">
         <f>IF(OR(E4="Muito baixo",E4="Baixo"),"pH","")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="H23" s="36">
+      <c r="H23" s="37">
         <f>IF(OR(E5="Muito baixo",E5="Baixo"),"Matéria Orgânica","")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="H24" s="36">
+      <c r="H24" s="37">
         <f>IF(OR(E6="Muito baixo",E6="Baixo"),"Fósforo","")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="H25" s="36">
+      <c r="H25" s="37">
         <f>IF(OR(E7="Muito baixo",E7="Baixo"),"Potássio","")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="H26" s="36">
+      <c r="H26" s="37">
         <f>IF(OR(E8="Muito baixo",E8="Baixo"),"Cálcio","")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="H27" s="36">
+      <c r="H27" s="37">
         <f>IF(OR(E9="Muito baixo",E9="Baixo"),"Magnésio","")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="H28" s="36">
+      <c r="H28" s="37">
         <f>IF(OR(E10="Muito baixo",E10="Baixo"),"V%","")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="H29" s="36">
+      <c r="H29" s="37">
         <f>IF(OR(E11="Alto",E11="Muito alto"),"m% (Al)","")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="H30" s="36">
+      <c r="H30" s="37">
         <f>IF(OR(E12="Muito baixo",E12="Baixo"),"Enxofre","")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="H31" s="36">
+      <c r="H31" s="37">
         <f>IF(OR(E13="Muito baixo",E13="Baixo"),"Zinco","")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="H32" s="36">
+      <c r="H32" s="37">
         <f>IF(OR(E14="Muito baixo",E14="Baixo"),"Cobre","")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="H33" s="36">
+      <c r="H33" s="37">
         <f>IF(OR(E15="Muito baixo",E15="Baixo"),"Manganês","")</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="H34" s="36">
+      <c r="H34" s="37">
         <f>IF(OR(E16="Muito baixo",E16="Baixo"),"Ferro","")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="H35" s="36">
+      <c r="H35" s="37">
         <f>IF(OR(E17="Muito baixo",E17="Baixo"),"Boro","")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="H36" s="36">
+      <c r="H36" s="37">
         <f>IF(OR(E18="Muito baixo",E18="Baixo"),"Molibdênio","")</f>
         <v/>
       </c>
@@ -8025,7 +8180,7 @@
           <t>CTC a pH 7,0 - T (mmolc/dm³)</t>
         </is>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="33">
         <f>'Dados de Entrada'!C44</f>
         <v/>
       </c>
@@ -8036,7 +8191,7 @@
           <t>Saturação por Bases atual - V1 (%)</t>
         </is>
       </c>
-      <c r="C5" s="37">
+      <c r="C5" s="38">
         <f>'Dados de Entrada'!C45</f>
         <v/>
       </c>
@@ -8047,7 +8202,7 @@
           <t>Alumínio trocável - Al³⁺ (mmolc/dm³)</t>
         </is>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="33">
         <f>'Dados de Entrada'!E30</f>
         <v/>
       </c>
@@ -8058,7 +8213,7 @@
           <t>Cálcio (Ca²⁺, mmolc/dm³)</t>
         </is>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="33">
         <f>'Dados de Entrada'!E28</f>
         <v/>
       </c>
@@ -8069,7 +8224,7 @@
           <t>Magnésio (Mg²⁺, mmolc/dm³)</t>
         </is>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <f>'Dados de Entrada'!E29</f>
         <v/>
       </c>
@@ -8080,7 +8235,7 @@
           <t>Teor de argila (%)</t>
         </is>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="38">
         <f>'Dados de Entrada'!C18</f>
         <v/>
       </c>
@@ -8091,7 +8246,7 @@
           <t>Estado (UF)</t>
         </is>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="39">
         <f>'Dados de Entrada'!C6</f>
         <v/>
       </c>
@@ -8102,7 +8257,7 @@
           <t>Cultura</t>
         </is>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="39">
         <f>'Dados de Entrada'!C8</f>
         <v/>
       </c>
@@ -8131,37 +8286,37 @@
           <t>V2 sugerido pela cultura (técnico)</t>
         </is>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="40">
         <f>IFERROR(INDEX(TAB_V2_CULTURA,MATCH(C11,INDEX(TAB_V2_CULTURA,0,1),0),2),70)</f>
         <v/>
       </c>
-      <c r="J15" s="40" t="inlineStr">
+      <c r="J15" s="41" t="inlineStr">
         <is>
           <t>Cultura</t>
         </is>
       </c>
-      <c r="K15" s="40" t="inlineStr">
+      <c r="K15" s="41" t="inlineStr">
         <is>
           <t>V2 alvo (%)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="41" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>V2 adotado no cálculo</t>
         </is>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="43">
         <f>IF(C13="",C15,C13)</f>
         <v/>
       </c>
-      <c r="J16" s="43" t="inlineStr">
+      <c r="J16" s="44" t="inlineStr">
         <is>
           <t>Soja</t>
         </is>
       </c>
-      <c r="K16" s="43" t="n">
+      <c r="K16" s="44" t="n">
         <v>70</v>
       </c>
     </row>
@@ -8171,26 +8326,26 @@
           <t>Estado é predominantemente Cerrado?</t>
         </is>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>IFERROR(VLOOKUP(C10,TAB_UF_CERRADO,2,FALSE),"Não")</f>
         <v/>
       </c>
-      <c r="J17" s="43" t="inlineStr">
+      <c r="J17" s="44" t="inlineStr">
         <is>
           <t>Milho</t>
         </is>
       </c>
-      <c r="K17" s="43" t="n">
+      <c r="K17" s="44" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="18">
-      <c r="J18" s="43" t="inlineStr">
+      <c r="J18" s="44" t="inlineStr">
         <is>
           <t>Sorgo</t>
         </is>
       </c>
-      <c r="K18" s="43" t="n">
+      <c r="K18" s="44" t="n">
         <v>60</v>
       </c>
     </row>
@@ -8200,12 +8355,12 @@
           <t>2. Resultado por método (todos calculados; consulte fonte e confiança)</t>
         </is>
       </c>
-      <c r="J19" s="43" t="inlineStr">
+      <c r="J19" s="44" t="inlineStr">
         <is>
           <t>Feijão</t>
         </is>
       </c>
-      <c r="K19" s="43" t="n">
+      <c r="K19" s="44" t="n">
         <v>70</v>
       </c>
     </row>
@@ -8235,30 +8390,30 @@
           <t>Confiança</t>
         </is>
       </c>
-      <c r="J20" s="43" t="inlineStr">
+      <c r="J20" s="44" t="inlineStr">
         <is>
           <t>Cana-de-açúcar</t>
         </is>
       </c>
-      <c r="K20" s="43" t="n">
+      <c r="K20" s="44" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="31" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Método da saturação por bases</t>
         </is>
       </c>
-      <c r="C21" s="44">
+      <c r="C21" s="45">
         <f>MAX(0,(C4*(C16-C5))/10)</f>
         <v/>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="40">
         <f>C12</f>
         <v/>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="46">
         <f>C21*(100/D21)</f>
         <v/>
       </c>
@@ -8267,30 +8422,30 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="J21" s="43" t="inlineStr">
+      <c r="J21" s="44" t="inlineStr">
         <is>
           <t>Pastagem Panicum</t>
         </is>
       </c>
-      <c r="K21" s="43" t="n">
+      <c r="K21" s="44" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="31" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>Método de neutralização do Alumínio tóxico (Kamprath)</t>
         </is>
       </c>
-      <c r="C22" s="44">
+      <c r="C22" s="45">
         <f>(C6/10)*2</f>
         <v/>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="40">
         <f>C12</f>
         <v/>
       </c>
-      <c r="E22" s="45">
+      <c r="E22" s="46">
         <f>C22*(100/D22)</f>
         <v/>
       </c>
@@ -8299,30 +8454,30 @@
           <t>Média</t>
         </is>
       </c>
-      <c r="J22" s="43" t="inlineStr">
+      <c r="J22" s="44" t="inlineStr">
         <is>
           <t>Pastagem Brachiaria</t>
         </is>
       </c>
-      <c r="K22" s="43" t="n">
+      <c r="K22" s="44" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="31" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>Método da neutralização do Al³⁺ + elevação de Ca²⁺ e Mg²⁺ (Cerrado)</t>
         </is>
       </c>
-      <c r="C23" s="44">
+      <c r="C23" s="45">
         <f>(C6/10)*2+MAX(0,2-((C7+C8)/10))</f>
         <v/>
       </c>
-      <c r="D23" s="39">
+      <c r="D23" s="40">
         <f>C12</f>
         <v/>
       </c>
-      <c r="E23" s="45">
+      <c r="E23" s="46">
         <f>C23*(100/D23)</f>
         <v/>
       </c>
@@ -8333,12 +8488,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="J24" s="40" t="inlineStr">
+      <c r="J24" s="41" t="inlineStr">
         <is>
           <t>UF</t>
         </is>
       </c>
-      <c r="K24" s="40" t="inlineStr">
+      <c r="K24" s="41" t="inlineStr">
         <is>
           <t>Bioma predominante Cerrado?</t>
         </is>
@@ -8350,75 +8505,75 @@
           <t>3. Escolha automática e recomendação final</t>
         </is>
       </c>
-      <c r="J25" s="43" t="inlineStr">
+      <c r="J25" s="44" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="K25" s="43" t="inlineStr">
+      <c r="K25" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="41" t="inlineStr">
+      <c r="B26" s="42" t="inlineStr">
         <is>
           <t>Método recomendado</t>
         </is>
       </c>
-      <c r="C26" s="46">
+      <c r="C26" s="47">
         <f>IF(C17="Sim","Método da neutralização do Al³⁺ + elevação de Ca²⁺ e Mg²⁺ (Cerrado)","Método da saturação por bases")</f>
         <v/>
       </c>
-      <c r="J26" s="43" t="inlineStr">
+      <c r="J26" s="44" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="K26" s="43" t="inlineStr">
+      <c r="K26" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="41" t="inlineStr">
+      <c r="B27" s="42" t="inlineStr">
         <is>
           <t>NC final corrigida pelo PRNT (t/ha)</t>
         </is>
       </c>
-      <c r="C27" s="47">
+      <c r="C27" s="48">
         <f>IF(C17="Sim",E23,E21)</f>
         <v/>
       </c>
-      <c r="J27" s="43" t="inlineStr">
+      <c r="J27" s="44" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="K27" s="43" t="inlineStr">
+      <c r="K27" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="41" t="inlineStr">
+      <c r="B28" s="42" t="inlineStr">
         <is>
           <t>Quantidade total para a área (t)</t>
         </is>
       </c>
-      <c r="C28" s="48">
+      <c r="C28" s="49">
         <f>C27*'Dados de Entrada'!C7</f>
         <v/>
       </c>
-      <c r="J28" s="43" t="inlineStr">
+      <c r="J28" s="44" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="K28" s="43" t="inlineStr">
+      <c r="K28" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
@@ -8434,12 +8589,12 @@
         <f>IF(C27&gt;5,"Aplicar em 2 vezes (metade agora incorporada, metade na safra seguinte) - dose elevada",IF(C27=0,"Sem necessidade de calagem","Aplicação única, incorporada"))</f>
         <v/>
       </c>
-      <c r="J29" s="43" t="inlineStr">
+      <c r="J29" s="44" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="K29" s="43" t="inlineStr">
+      <c r="K29" s="44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -8451,52 +8606,52 @@
           <t>Justificativa técnica</t>
         </is>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="31">
         <f>IF(C17="Sim","Estado de Cerrado típico: prioriza-se o método de neutralização do Al³⁺ e elevação de Ca+Mg (Sousa &amp; Lobato, 2004), adequado a Latossolos/Oxissolos com CTC baixa e Al tóxico.","Fora do Cerrado típico: prioriza-se o método da saturação por bases (Raij et al., Boletim 100), tradicionalmente usado em SP/MG/ES para culturas anuais.")</f>
         <v/>
       </c>
-      <c r="J30" s="43" t="inlineStr">
+      <c r="J30" s="44" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="K30" s="43" t="inlineStr">
+      <c r="K30" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="J31" s="43" t="inlineStr">
+      <c r="J31" s="44" t="inlineStr">
         <is>
           <t>DF</t>
         </is>
       </c>
-      <c r="K31" s="43" t="inlineStr">
+      <c r="K31" s="44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="J32" s="43" t="inlineStr">
+      <c r="J32" s="44" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="K32" s="43" t="inlineStr">
+      <c r="K32" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="J33" s="43" t="inlineStr">
+      <c r="J33" s="44" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="K33" s="43" t="inlineStr">
+      <c r="K33" s="44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -8508,225 +8663,225 @@
           <t>Nível de confiança da recomendação final</t>
         </is>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="31">
         <f>IF(C17="Sim","Alta (fórmula e critério de aplicação confirmados - Sousa &amp; Lobato, 2004)","Alta (fórmula confirmada - Raij et al., Boletim 100, 1997)")</f>
         <v/>
       </c>
-      <c r="J34" s="43" t="inlineStr">
+      <c r="J34" s="44" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="K34" s="43" t="inlineStr">
+      <c r="K34" s="44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="J35" s="43" t="inlineStr">
+      <c r="J35" s="44" t="inlineStr">
         <is>
           <t>MT</t>
         </is>
       </c>
-      <c r="K35" s="43" t="inlineStr">
+      <c r="K35" s="44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>Os 3 métodos são sempre calculados e exibidos (transparência total). A escolha automática segue a convenção regional consolidada na literatura agronômica brasileira; o técnico responsável pode adotar outro método manualmente, se justificado pelas condições locais.</t>
         </is>
       </c>
-      <c r="J36" s="43" t="inlineStr">
+      <c r="J36" s="44" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="K36" s="43" t="inlineStr">
+      <c r="K36" s="44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="J37" s="43" t="inlineStr">
+      <c r="J37" s="44" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="K37" s="43" t="inlineStr">
+      <c r="K37" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="J38" s="43" t="inlineStr">
+      <c r="J38" s="44" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="K38" s="43" t="inlineStr">
+      <c r="K38" s="44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="J39" s="43" t="inlineStr">
+      <c r="J39" s="44" t="inlineStr">
         <is>
           <t>PB</t>
         </is>
       </c>
-      <c r="K39" s="43" t="inlineStr">
+      <c r="K39" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="J40" s="43" t="inlineStr">
+      <c r="J40" s="44" t="inlineStr">
         <is>
           <t>PR</t>
         </is>
       </c>
-      <c r="K40" s="43" t="inlineStr">
+      <c r="K40" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="J41" s="43" t="inlineStr">
+      <c r="J41" s="44" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="K41" s="43" t="inlineStr">
+      <c r="K41" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="J42" s="43" t="inlineStr">
+      <c r="J42" s="44" t="inlineStr">
         <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="K42" s="43" t="inlineStr">
+      <c r="K42" s="44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="J43" s="43" t="inlineStr">
+      <c r="J43" s="44" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K43" s="43" t="inlineStr">
+      <c r="K43" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="J44" s="43" t="inlineStr">
+      <c r="J44" s="44" t="inlineStr">
         <is>
           <t>RN</t>
         </is>
       </c>
-      <c r="K44" s="43" t="inlineStr">
+      <c r="K44" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="J45" s="43" t="inlineStr">
+      <c r="J45" s="44" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="K45" s="43" t="inlineStr">
+      <c r="K45" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="J46" s="43" t="inlineStr">
+      <c r="J46" s="44" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="K46" s="43" t="inlineStr">
+      <c r="K46" s="44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="J47" s="43" t="inlineStr">
+      <c r="J47" s="44" t="inlineStr">
         <is>
           <t>RR</t>
         </is>
       </c>
-      <c r="K47" s="43" t="inlineStr">
+      <c r="K47" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="J48" s="43" t="inlineStr">
+      <c r="J48" s="44" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="K48" s="43" t="inlineStr">
+      <c r="K48" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="J49" s="43" t="inlineStr">
+      <c r="J49" s="44" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="K49" s="43" t="inlineStr">
+      <c r="K49" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="J50" s="43" t="inlineStr">
+      <c r="J50" s="44" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="K50" s="43" t="inlineStr">
+      <c r="K50" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="J51" s="43" t="inlineStr">
+      <c r="J51" s="44" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="K51" s="43" t="inlineStr">
+      <c r="K51" s="44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -8795,7 +8950,7 @@
           <t>Teor de argila (%)</t>
         </is>
       </c>
-      <c r="C4" s="37">
+      <c r="C4" s="38">
         <f>'Dados de Entrada'!C18</f>
         <v/>
       </c>
@@ -8806,7 +8961,7 @@
           <t>Saturação por Alumínio m% - camada amostrada</t>
         </is>
       </c>
-      <c r="C5" s="37">
+      <c r="C5" s="38">
         <f>'Dados de Entrada'!C46</f>
         <v/>
       </c>
@@ -8817,7 +8972,7 @@
           <t>Cálcio (Ca²⁺, mmolc/dm³) - camada amostrada</t>
         </is>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="33">
         <f>'Dados de Entrada'!E28</f>
         <v/>
       </c>
@@ -8828,7 +8983,7 @@
           <t>Cultura</t>
         </is>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="39">
         <f>'Dados de Entrada'!C8</f>
         <v/>
       </c>
@@ -8862,7 +9017,7 @@
           <t>m% efetivo considerado</t>
         </is>
       </c>
-      <c r="C12" s="49">
+      <c r="C12" s="50">
         <f>IF(C8="",C5,C8)</f>
         <v/>
       </c>
@@ -8873,7 +9028,7 @@
           <t>Ca²⁺ efetivo considerado (mmolc/dm³)</t>
         </is>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="45">
         <f>IF(C9="",C6,C9)</f>
         <v/>
       </c>
@@ -8884,18 +9039,18 @@
           <t>Camada usada no critério</t>
         </is>
       </c>
-      <c r="C14" s="43">
+      <c r="C14" s="44">
         <f>IF(AND(C8="",C9=""),"Camada amostrada (aproximação)","20-40 cm (informada)")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="41" t="inlineStr">
+      <c r="B15" s="42" t="inlineStr">
         <is>
           <t>Recomenda-se gesso?</t>
         </is>
       </c>
-      <c r="C15" s="50">
+      <c r="C15" s="51">
         <f>IF(OR(C12&gt;20,C13&lt;5),"Sim","Não")</f>
         <v/>
       </c>
@@ -8906,7 +9061,7 @@
           <t>Critério atendido</t>
         </is>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <f>IF(C15="Não","Nenhum critério de gessagem atendido",_xlfn.TEXTJOIN("; ",TRUE,IF(C12&gt;20,"m% &gt; 20%",""),IF(C13&lt;5,"Ca²⁺ &lt; 0,5 cmolc/dm³ (5 mmolc/dm³)","")))</f>
         <v/>
       </c>
@@ -8924,29 +9079,29 @@
           <t>Cultura perene (fator 75) ou anual (fator 50)?</t>
         </is>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="32">
         <f>IF(OR(C7="Cana-de-açúcar",C7="Pastagem Panicum",C7="Pastagem Brachiaria"),"Perene (75)","Anual (50)")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="41" t="inlineStr">
+      <c r="B20" s="42" t="inlineStr">
         <is>
           <t>Dose de gesso agrícola (kg/ha)</t>
         </is>
       </c>
-      <c r="C20" s="51">
+      <c r="C20" s="52">
         <f>IF(C15="Não",0,IF(C19="Perene (75)",75,50)*C4)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="41" t="inlineStr">
+      <c r="B21" s="42" t="inlineStr">
         <is>
           <t>Dose total para a área (t)</t>
         </is>
       </c>
-      <c r="C21" s="48">
+      <c r="C21" s="49">
         <f>C20/1000*'Dados de Entrada'!C7</f>
         <v/>
       </c>
@@ -8957,7 +9112,7 @@
           <t>Enxofre suprido pelo gesso (kg S/ha)</t>
         </is>
       </c>
-      <c r="C22" s="52">
+      <c r="C22" s="53">
         <f>C20*0.15</f>
         <v/>
       </c>
@@ -8968,7 +9123,7 @@
           <t>Cálcio suprido pelo gesso (kg Ca/ha)</t>
         </is>
       </c>
-      <c r="C23" s="52">
+      <c r="C23" s="53">
         <f>C20*0.16</f>
         <v/>
       </c>
@@ -8979,7 +9134,7 @@
           <t>Recomendação de parcelamento/logística</t>
         </is>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <f>IF(C20=0,"Sem necessidade de gesso",IF(C20&gt;2000,"Dose elevada - avaliar parcelamento em 2 aplicações e revisão técnica em campo","Aplicação única, a lanço, sem incorporação obrigatória"))</f>
         <v/>
       </c>
@@ -8992,7 +9147,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="30" t="inlineStr">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>Fórmula e critério: Sousa, D.M.G.; Lobato, E. Uso de Gesso Agrícola nos Solos do Cerrado. Circular Técnica 32, Embrapa Cerrados, 2004/2005.
 Confiança: Alta (fórmula e critério qualitativo); Média (limiar exato de Ca subsuperficial, que varia entre 0,2-0,5 cmolc/dm³ conforme a fonte secundária consultada).
@@ -9047,8 +9202,10 @@
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="55" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -9059,7 +9216,7 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Tabela editável. Soja e Milho possuem também extração total (não só exportação pelo grão), usada na aba de cada cultura para estimar o retorno de nutrientes via palhada/resíduo. Fonte e confiança por cultura na coluna Q/R.</t>
         </is>
@@ -9168,64 +9325,64 @@
           <t>Soja</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>sc/ha (60 kg)</t>
         </is>
       </c>
-      <c r="D6" s="39" t="n">
+      <c r="D6" s="40" t="n">
         <v>60</v>
       </c>
-      <c r="E6" s="39" t="n">
+      <c r="E6" s="40" t="n">
         <v>70</v>
       </c>
-      <c r="F6" s="53" t="n">
+      <c r="F6" s="54" t="n">
         <v>50</v>
       </c>
-      <c r="G6" s="53" t="n">
+      <c r="G6" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="H6" s="53" t="n">
+      <c r="H6" s="54" t="n">
         <v>20</v>
       </c>
-      <c r="I6" s="53" t="n">
+      <c r="I6" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="J6" s="53" t="n">
+      <c r="J6" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="53" t="n">
+      <c r="K6" s="54" t="n">
         <v>2.5</v>
       </c>
-      <c r="L6" s="53" t="n">
+      <c r="L6" s="54" t="n">
         <v>0.02</v>
       </c>
-      <c r="M6" s="53" t="n">
+      <c r="M6" s="54" t="n">
         <v>0.03</v>
       </c>
-      <c r="N6" s="53" t="n">
+      <c r="N6" s="54" t="n">
         <v>0.008</v>
       </c>
-      <c r="O6" s="53" t="n">
+      <c r="O6" s="54" t="n">
         <v>0.04</v>
       </c>
-      <c r="P6" s="53" t="n">
+      <c r="P6" s="54" t="n">
         <v>80</v>
       </c>
-      <c r="Q6" s="53" t="n">
+      <c r="Q6" s="54" t="n">
         <v>16</v>
       </c>
-      <c r="R6" s="53" t="n">
+      <c r="R6" s="54" t="n">
         <v>40</v>
       </c>
-      <c r="S6" s="27" t="inlineStr">
-        <is>
-          <t>Sfredo, G.J. Soja no Brasil: calagem, adubação e nutrição mineral. Documentos 305, Embrapa Soja, 2008; valores consolidados também em Malavolta (2006) e boletins técnicos de manejo de fertilidade.</t>
-        </is>
-      </c>
-      <c r="T6" s="27" t="inlineStr">
-        <is>
-          <t>Média (variação relevante relatada entre fontes, sobretudo para K em altas produtividades - efeito de diluição já discutido por Zanon et al. em curvas de resposta a potássio).</t>
+      <c r="S6" s="26" t="inlineStr">
+        <is>
+          <t>Sfredo (2008), Embrapa Soja</t>
+        </is>
+      </c>
+      <c r="T6" s="26" t="inlineStr">
+        <is>
+          <t>Média</t>
         </is>
       </c>
     </row>
@@ -9235,64 +9392,64 @@
           <t>Milho</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>sc/ha (60 kg)</t>
         </is>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="40" t="n">
         <v>60</v>
       </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="40" t="n">
         <v>70</v>
       </c>
-      <c r="F7" s="53" t="n">
+      <c r="F7" s="54" t="n">
         <v>14</v>
       </c>
-      <c r="G7" s="53" t="n">
+      <c r="G7" s="54" t="n">
         <v>7</v>
       </c>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="54" t="n">
         <v>4.5</v>
       </c>
-      <c r="I7" s="53" t="n">
+      <c r="I7" s="54" t="n">
         <v>1.5</v>
       </c>
-      <c r="J7" s="53" t="n">
+      <c r="J7" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="53" t="n">
+      <c r="K7" s="54" t="n">
         <v>1.2</v>
       </c>
-      <c r="L7" s="53" t="n">
+      <c r="L7" s="54" t="n">
         <v>0.006</v>
       </c>
-      <c r="M7" s="53" t="n">
+      <c r="M7" s="54" t="n">
         <v>0.015</v>
       </c>
-      <c r="N7" s="53" t="n">
+      <c r="N7" s="54" t="n">
         <v>0.004</v>
       </c>
-      <c r="O7" s="53" t="n">
+      <c r="O7" s="54" t="n">
         <v>0.025</v>
       </c>
-      <c r="P7" s="53" t="n">
+      <c r="P7" s="54" t="n">
         <v>22</v>
       </c>
-      <c r="Q7" s="53" t="n">
+      <c r="Q7" s="54" t="n">
         <v>9</v>
       </c>
-      <c r="R7" s="53" t="n">
+      <c r="R7" s="54" t="n">
         <v>20</v>
       </c>
-      <c r="S7" s="27" t="inlineStr">
-        <is>
-          <t>Coelho, A.M. Nutrição e Adubação do Milho. Circular Técnica 78, Embrapa Milho e Sorgo, 2006 (valores 'clássicos' de exportação pelo grão).</t>
-        </is>
-      </c>
-      <c r="T7" s="27" t="inlineStr">
-        <is>
-          <t>Média (circulares mais recentes revisam alguns coeficientes; verificar se tratam de grão isolado ou planta inteira/silagem antes de adotar valores diferentes).</t>
+      <c r="S7" s="26" t="inlineStr">
+        <is>
+          <t>Coelho (2006), Embrapa Milho e Sorgo</t>
+        </is>
+      </c>
+      <c r="T7" s="26" t="inlineStr">
+        <is>
+          <t>Média</t>
         </is>
       </c>
     </row>
@@ -9302,56 +9459,56 @@
           <t>Sorgo</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>sc/ha (60 kg)</t>
         </is>
       </c>
-      <c r="D8" s="39" t="n">
+      <c r="D8" s="40" t="n">
         <v>60</v>
       </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="40" t="n">
         <v>60</v>
       </c>
-      <c r="F8" s="53" t="n">
+      <c r="F8" s="54" t="n">
         <v>18</v>
       </c>
-      <c r="G8" s="53" t="n">
+      <c r="G8" s="54" t="n">
         <v>7</v>
       </c>
-      <c r="H8" s="53" t="n">
+      <c r="H8" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="I8" s="53" t="n">
+      <c r="I8" s="54" t="n">
         <v>1.8</v>
       </c>
-      <c r="J8" s="53" t="n">
+      <c r="J8" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="K8" s="53" t="n">
+      <c r="K8" s="54" t="n">
         <v>1.3</v>
       </c>
-      <c r="L8" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="31" t="inlineStr"/>
-      <c r="Q8" s="31" t="inlineStr"/>
-      <c r="R8" s="31" t="inlineStr"/>
-      <c r="S8" s="27" t="inlineStr">
-        <is>
-          <t>Valores de referência consolidados na prática agronômica (perfil nutricional próximo ao do milho, cultura de mesma família); ajustar com boletim regional (Embrapa Milho e Sorgo) quando disponível.</t>
-        </is>
-      </c>
-      <c r="T8" s="27" t="inlineStr">
+      <c r="L8" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="32" t="inlineStr"/>
+      <c r="Q8" s="32" t="inlineStr"/>
+      <c r="R8" s="32" t="inlineStr"/>
+      <c r="S8" s="26" t="inlineStr">
+        <is>
+          <t>Estimativa por analogia c/ milho</t>
+        </is>
+      </c>
+      <c r="T8" s="26" t="inlineStr">
         <is>
           <t>Baixa-Média</t>
         </is>
@@ -9363,56 +9520,56 @@
           <t>Feijão</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>sc/ha (60 kg)</t>
         </is>
       </c>
-      <c r="D9" s="39" t="n">
+      <c r="D9" s="40" t="n">
         <v>60</v>
       </c>
-      <c r="E9" s="39" t="n">
+      <c r="E9" s="40" t="n">
         <v>70</v>
       </c>
-      <c r="F9" s="53" t="n">
+      <c r="F9" s="54" t="n">
         <v>45</v>
       </c>
-      <c r="G9" s="53" t="n">
+      <c r="G9" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="H9" s="53" t="n">
+      <c r="H9" s="54" t="n">
         <v>25</v>
       </c>
-      <c r="I9" s="53" t="n">
+      <c r="I9" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="53" t="n">
+      <c r="J9" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="53" t="n">
+      <c r="K9" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="31" t="inlineStr"/>
-      <c r="Q9" s="31" t="inlineStr"/>
-      <c r="R9" s="31" t="inlineStr"/>
-      <c r="S9" s="27" t="inlineStr">
-        <is>
-          <t>Valores de referência consolidados na prática agronômica brasileira (perfil leguminosa, próximo à soja em proporção, porém com ciclo mais curto e menor fixação biológica líquida). Ajustar com boletim regional (IAC/Embrapa Arroz e Feijão) quando disponível.</t>
-        </is>
-      </c>
-      <c r="T9" s="27" t="inlineStr">
+      <c r="L9" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="32" t="inlineStr"/>
+      <c r="Q9" s="32" t="inlineStr"/>
+      <c r="R9" s="32" t="inlineStr"/>
+      <c r="S9" s="26" t="inlineStr">
+        <is>
+          <t>Estimativa por analogia c/ soja</t>
+        </is>
+      </c>
+      <c r="T9" s="26" t="inlineStr">
         <is>
           <t>Baixa-Média</t>
         </is>
@@ -9424,56 +9581,56 @@
           <t>Cana-de-açúcar</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>t/ha</t>
         </is>
       </c>
-      <c r="D10" s="39" t="n">
+      <c r="D10" s="40" t="n">
         <v>1000</v>
       </c>
-      <c r="E10" s="39" t="n">
+      <c r="E10" s="40" t="n">
         <v>60</v>
       </c>
-      <c r="F10" s="53" t="n">
+      <c r="F10" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="53" t="n">
+      <c r="G10" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="H10" s="53" t="n">
+      <c r="H10" s="54" t="n">
         <v>1.7</v>
       </c>
-      <c r="I10" s="53" t="n">
+      <c r="I10" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="J10" s="53" t="n">
+      <c r="J10" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="K10" s="53" t="n">
+      <c r="K10" s="54" t="n">
         <v>0.4</v>
       </c>
-      <c r="L10" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="31" t="inlineStr"/>
-      <c r="Q10" s="31" t="inlineStr"/>
-      <c r="R10" s="31" t="inlineStr"/>
-      <c r="S10" s="27" t="inlineStr">
-        <is>
-          <t>Valores de referência consolidados na prática agronômica (exportação por tonelada de colmo); ajustar com Boletim 200/Fundação MT ou boletim regional do setor sucroenergético quando disponível.</t>
-        </is>
-      </c>
-      <c r="T10" s="27" t="inlineStr">
+      <c r="L10" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="32" t="inlineStr"/>
+      <c r="Q10" s="32" t="inlineStr"/>
+      <c r="R10" s="32" t="inlineStr"/>
+      <c r="S10" s="26" t="inlineStr">
+        <is>
+          <t>Estimativa - validar c/ Boletim 200/Fundação MT</t>
+        </is>
+      </c>
+      <c r="T10" s="26" t="inlineStr">
         <is>
           <t>Baixa-Média</t>
         </is>
@@ -9485,56 +9642,56 @@
           <t>Pastagem Panicum</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>t MS/ha</t>
         </is>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D11" s="40" t="n">
         <v>1000</v>
       </c>
-      <c r="E11" s="39" t="n">
+      <c r="E11" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="53" t="n">
+      <c r="F11" s="54" t="n">
         <v>15</v>
       </c>
-      <c r="G11" s="53" t="n">
+      <c r="G11" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="53" t="n">
+      <c r="H11" s="54" t="n">
         <v>18</v>
       </c>
-      <c r="I11" s="53" t="n">
+      <c r="I11" s="54" t="n">
         <v>1.5</v>
       </c>
-      <c r="J11" s="53" t="n">
+      <c r="J11" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="53" t="n">
+      <c r="K11" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="L11" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="31" t="inlineStr"/>
-      <c r="Q11" s="31" t="inlineStr"/>
-      <c r="R11" s="31" t="inlineStr"/>
-      <c r="S11" s="27" t="inlineStr">
-        <is>
-          <t>Valores de referência consolidados na prática agronômica para exportação por tonelada de matéria seca em pastagens tropicais (Panicum maximum); ajustar com boletim regional (Embrapa Gado de Corte) quando disponível.</t>
-        </is>
-      </c>
-      <c r="T11" s="27" t="inlineStr">
+      <c r="L11" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="32" t="inlineStr"/>
+      <c r="Q11" s="32" t="inlineStr"/>
+      <c r="R11" s="32" t="inlineStr"/>
+      <c r="S11" s="26" t="inlineStr">
+        <is>
+          <t>Estimativa - validar c/ Embrapa Gado de Corte</t>
+        </is>
+      </c>
+      <c r="T11" s="26" t="inlineStr">
         <is>
           <t>Baixa-Média</t>
         </is>
@@ -9546,56 +9703,56 @@
           <t>Pastagem Brachiaria</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>t MS/ha</t>
         </is>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D12" s="40" t="n">
         <v>1000</v>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E12" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="F12" s="53" t="n">
+      <c r="F12" s="54" t="n">
         <v>13</v>
       </c>
-      <c r="G12" s="53" t="n">
+      <c r="G12" s="54" t="n">
         <v>3.5</v>
       </c>
-      <c r="H12" s="53" t="n">
+      <c r="H12" s="54" t="n">
         <v>15</v>
       </c>
-      <c r="I12" s="53" t="n">
+      <c r="I12" s="54" t="n">
         <v>1.3</v>
       </c>
-      <c r="J12" s="53" t="n">
+      <c r="J12" s="54" t="n">
         <v>2.5</v>
       </c>
-      <c r="K12" s="53" t="n">
+      <c r="K12" s="54" t="n">
         <v>1.8</v>
       </c>
-      <c r="L12" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="31" t="inlineStr"/>
-      <c r="Q12" s="31" t="inlineStr"/>
-      <c r="R12" s="31" t="inlineStr"/>
-      <c r="S12" s="27" t="inlineStr">
-        <is>
-          <t>Valores de referência consolidados na prática agronômica para exportação por tonelada de matéria seca em pastagens tropicais (Brachiaria/Urochloa spp.); ajustar com boletim regional (Embrapa Gado de Corte) quando disponível.</t>
-        </is>
-      </c>
-      <c r="T12" s="27" t="inlineStr">
+      <c r="L12" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="32" t="inlineStr"/>
+      <c r="Q12" s="32" t="inlineStr"/>
+      <c r="R12" s="32" t="inlineStr"/>
+      <c r="S12" s="26" t="inlineStr">
+        <is>
+          <t>Estimativa - validar c/ Embrapa Gado de Corte</t>
+        </is>
+      </c>
+      <c r="T12" s="26" t="inlineStr">
         <is>
           <t>Baixa-Média</t>
         </is>
@@ -9609,7 +9766,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>A recomendação de P e K desta planilha NÃO usa uma tabela fixa de doses. Ela calcula: dose de manutenção = (exportação pela produtividade meta) / (eficiência de aproveitamento do fertilizante, que depende da textura do solo) - e então aplica um fator de ajuste conforme a classe de fertilidade atual do solo (constrói fertilidade em solos pobres, reduz em solos já ricos). Isso integra análise de solo, textura, produtividade e exportação em vez de uma tabela estática. Os fatores abaixo são premissas explícitas e editáveis - não substituem curvas de resposta calibradas localmente.</t>
         </is>
@@ -9640,10 +9797,10 @@
           <t>Arenoso (&lt; 15% argila)</t>
         </is>
       </c>
-      <c r="C20" s="54" t="n">
+      <c r="C20" s="55" t="n">
         <v>0.35</v>
       </c>
-      <c r="D20" s="54" t="n">
+      <c r="D20" s="55" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -9653,10 +9810,10 @@
           <t>Textura média (15-35% argila)</t>
         </is>
       </c>
-      <c r="C21" s="54" t="n">
+      <c r="C21" s="55" t="n">
         <v>0.25</v>
       </c>
-      <c r="D21" s="54" t="n">
+      <c r="D21" s="55" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -9666,10 +9823,10 @@
           <t>Argiloso (&gt; 35% argila)</t>
         </is>
       </c>
-      <c r="C22" s="54" t="n">
+      <c r="C22" s="55" t="n">
         <v>0.15</v>
       </c>
-      <c r="D22" s="54" t="n">
+      <c r="D22" s="55" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -9768,7 +9925,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="36">
+      <c r="A33" s="37">
         <f>B33&amp;"|"&amp;C33</f>
         <v/>
       </c>
@@ -9785,14 +9942,14 @@
       <c r="D33" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="E33" s="43" t="inlineStr">
+      <c r="E33" s="44" t="inlineStr">
         <is>
           <t>Boletim 100 (síntese secundária) - Confiança Média</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="36">
+      <c r="A34" s="37">
         <f>B34&amp;"|"&amp;C34</f>
         <v/>
       </c>
@@ -9809,14 +9966,14 @@
       <c r="D34" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="43" t="inlineStr">
+      <c r="E34" s="44" t="inlineStr">
         <is>
           <t>Boletim 100 (síntese secundária) - Confiança Média</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="36">
+      <c r="A35" s="37">
         <f>B35&amp;"|"&amp;C35</f>
         <v/>
       </c>
@@ -9833,14 +9990,14 @@
       <c r="D35" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="43" t="inlineStr">
+      <c r="E35" s="44" t="inlineStr">
         <is>
           <t>Sem necessidade</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="36">
+      <c r="A36" s="37">
         <f>B36&amp;"|"&amp;C36</f>
         <v/>
       </c>
@@ -9857,14 +10014,14 @@
       <c r="D36" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E36" s="43" t="inlineStr">
+      <c r="E36" s="44" t="inlineStr">
         <is>
           <t>Boletim 100 (síntese secundária) - Confiança Média</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="36">
+      <c r="A37" s="37">
         <f>B37&amp;"|"&amp;C37</f>
         <v/>
       </c>
@@ -9881,14 +10038,14 @@
       <c r="D37" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="E37" s="43" t="inlineStr">
+      <c r="E37" s="44" t="inlineStr">
         <is>
           <t>Estimativa de uso corrente - Confiança Baixa</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="36">
+      <c r="A38" s="37">
         <f>B38&amp;"|"&amp;C38</f>
         <v/>
       </c>
@@ -9905,14 +10062,14 @@
       <c r="D38" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="43" t="inlineStr">
+      <c r="E38" s="44" t="inlineStr">
         <is>
           <t>Sem necessidade</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="36">
+      <c r="A39" s="37">
         <f>B39&amp;"|"&amp;C39</f>
         <v/>
       </c>
@@ -9929,14 +10086,14 @@
       <c r="D39" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="E39" s="43" t="inlineStr">
+      <c r="E39" s="44" t="inlineStr">
         <is>
           <t>Estimativa de uso corrente - Confiança Baixa</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="36">
+      <c r="A40" s="37">
         <f>B40&amp;"|"&amp;C40</f>
         <v/>
       </c>
@@ -9953,14 +10110,14 @@
       <c r="D40" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="43" t="inlineStr">
+      <c r="E40" s="44" t="inlineStr">
         <is>
           <t>Estimativa de uso corrente - Confiança Baixa</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="36">
+      <c r="A41" s="37">
         <f>B41&amp;"|"&amp;C41</f>
         <v/>
       </c>
@@ -9977,14 +10134,14 @@
       <c r="D41" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="43" t="inlineStr">
+      <c r="E41" s="44" t="inlineStr">
         <is>
           <t>Sem necessidade</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="36">
+      <c r="A42" s="37">
         <f>B42&amp;"|"&amp;C42</f>
         <v/>
       </c>
@@ -10001,14 +10158,14 @@
       <c r="D42" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="E42" s="43" t="inlineStr">
+      <c r="E42" s="44" t="inlineStr">
         <is>
           <t>Estimativa de uso corrente - Confiança Baixa (Mn frequentemente via foliar)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="36">
+      <c r="A43" s="37">
         <f>B43&amp;"|"&amp;C43</f>
         <v/>
       </c>
@@ -10025,14 +10182,14 @@
       <c r="D43" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="E43" s="43" t="inlineStr">
+      <c r="E43" s="44" t="inlineStr">
         <is>
           <t>Estimativa de uso corrente - Confiança Baixa</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="36">
+      <c r="A44" s="37">
         <f>B44&amp;"|"&amp;C44</f>
         <v/>
       </c>
@@ -10049,14 +10206,14 @@
       <c r="D44" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="43" t="inlineStr">
+      <c r="E44" s="44" t="inlineStr">
         <is>
           <t>Sem necessidade</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="36">
+      <c r="A45" s="37">
         <f>B45&amp;"|"&amp;C45</f>
         <v/>
       </c>
@@ -10073,14 +10230,14 @@
       <c r="D45" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="E45" s="43" t="inlineStr">
+      <c r="E45" s="44" t="inlineStr">
         <is>
           <t>Aplicação usual via tratamento de sementes (g/ha) - Confiança Baixa</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="36">
+      <c r="A46" s="37">
         <f>B46&amp;"|"&amp;C46</f>
         <v/>
       </c>
@@ -10097,14 +10254,14 @@
       <c r="D46" s="26" t="n">
         <v>0.02</v>
       </c>
-      <c r="E46" s="43" t="inlineStr">
+      <c r="E46" s="44" t="inlineStr">
         <is>
           <t>Aplicação usual via tratamento de sementes (g/ha) - Confiança Baixa</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="36">
+      <c r="A47" s="37">
         <f>B47&amp;"|"&amp;C47</f>
         <v/>
       </c>
@@ -10121,7 +10278,7 @@
       <c r="D47" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="43" t="inlineStr">
+      <c r="E47" s="44" t="inlineStr">
         <is>
           <t>Sem necessidade</t>
         </is>
@@ -10150,6 +10307,7 @@
     <mergeCell ref="E36:H36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -10191,18 +10349,18 @@
           <t>Cultura selecionada em Dados de Entrada</t>
         </is>
       </c>
-      <c r="C4" s="38">
+      <c r="C4" s="39">
         <f>'Dados de Entrada'!C8</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Alerta</t>
         </is>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>IF(C4&lt;&gt;"Soja","A cultura em Dados de Entrada não é Soja - ajuste antes de usar esta aba","OK")</f>
         <v/>
       </c>
@@ -10213,7 +10371,7 @@
           <t>Área (ha)</t>
         </is>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="56">
         <f>'Dados de Entrada'!C7</f>
         <v/>
       </c>
@@ -10224,7 +10382,7 @@
           <t>Produtividade esperada</t>
         </is>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="38">
         <f>'Dados de Entrada'!C9</f>
         <v/>
       </c>
@@ -10235,7 +10393,7 @@
           <t>Unidade</t>
         </is>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="39">
         <f>'Dados de Entrada'!C10</f>
         <v/>
       </c>
@@ -10246,7 +10404,7 @@
           <t>Classe textural</t>
         </is>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="39">
         <f>'Dados de Entrada'!C19</f>
         <v/>
       </c>
@@ -10257,7 +10415,7 @@
           <t>Matéria Orgânica (g/dm³)</t>
         </is>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="33">
         <f>'Dados de Entrada'!E25</f>
         <v/>
       </c>
@@ -10268,18 +10426,18 @@
           <t>Sistema de plantio</t>
         </is>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="39">
         <f>'Dados de Entrada'!C12</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="41" t="inlineStr">
+      <c r="B12" s="42" t="inlineStr">
         <is>
           <t>Produtividade meta em t/ha</t>
         </is>
       </c>
-      <c r="C12" s="56">
+      <c r="C12" s="57">
         <f>C7*VLOOKUP("Soja",TAB_CULTURAS,3,FALSE)/1000</f>
         <v/>
       </c>
@@ -10297,7 +10455,7 @@
           <t>Classe - Fósforo</t>
         </is>
       </c>
-      <c r="C15" s="57">
+      <c r="C15" s="58">
         <f>Interpretação!E6</f>
         <v/>
       </c>
@@ -10308,7 +10466,7 @@
           <t>Classe - Potássio</t>
         </is>
       </c>
-      <c r="C16" s="57">
+      <c r="C16" s="58">
         <f>Interpretação!E7</f>
         <v/>
       </c>
@@ -10319,7 +10477,7 @@
           <t>Classe - Cálcio</t>
         </is>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="58">
         <f>Interpretação!E8</f>
         <v/>
       </c>
@@ -10330,7 +10488,7 @@
           <t>Classe - Magnésio</t>
         </is>
       </c>
-      <c r="C18" s="57">
+      <c r="C18" s="58">
         <f>Interpretação!E9</f>
         <v/>
       </c>
@@ -10341,7 +10499,7 @@
           <t>Classe - Enxofre</t>
         </is>
       </c>
-      <c r="C19" s="57">
+      <c r="C19" s="58">
         <f>Interpretação!E12</f>
         <v/>
       </c>
@@ -10352,7 +10510,7 @@
           <t>Classe - Zinco</t>
         </is>
       </c>
-      <c r="C20" s="57">
+      <c r="C20" s="58">
         <f>Interpretação!E13</f>
         <v/>
       </c>
@@ -10363,7 +10521,7 @@
           <t>Classe - Boro</t>
         </is>
       </c>
-      <c r="C21" s="57">
+      <c r="C21" s="58">
         <f>Interpretação!E17</f>
         <v/>
       </c>
@@ -10374,7 +10532,7 @@
           <t>Classe - Cobre</t>
         </is>
       </c>
-      <c r="C22" s="57">
+      <c r="C22" s="58">
         <f>Interpretação!E14</f>
         <v/>
       </c>
@@ -10385,7 +10543,7 @@
           <t>Classe - Manganês</t>
         </is>
       </c>
-      <c r="C23" s="57">
+      <c r="C23" s="58">
         <f>Interpretação!E15</f>
         <v/>
       </c>
@@ -10396,7 +10554,7 @@
           <t>Classe - Molibdênio</t>
         </is>
       </c>
-      <c r="C24" s="57">
+      <c r="C24" s="58">
         <f>Interpretação!E18</f>
         <v/>
       </c>
@@ -10411,30 +10569,29 @@
     <row r="27">
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Inoculação com Bradyrhizobium realizada corretamente?</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+          <t>Inoculação com Bradyrhizobium realizada corretamente? (Dados de Entrada)</t>
+        </is>
+      </c>
+      <c r="C27" s="39">
+        <f>'Dados de Entrada'!C49</f>
+        <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="41" t="inlineStr">
+      <c r="B28" s="42" t="inlineStr">
         <is>
           <t>Nitrogênio recomendado (kg N/ha)</t>
         </is>
       </c>
-      <c r="C28" s="58">
-        <f>IF(C27="Sim",0,C12*VLOOKUP("Soja",TAB_CULTURAS,5,FALSE)/0.5)</f>
+      <c r="C28" s="59">
+        <f>IF(C27="Sim",0,C12*VLOOKUP("Soja",TAB_CULTURAS,5,FALSE)/'Dados de Entrada'!C51)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="30" t="inlineStr">
-        <is>
-          <t>Fonte/Confiança: Alta - Embrapa Soja (doutrina consolidada): soja bem inoculada com Bradyrhizobium não responde economicamente à adubação nitrogenada mineral, mesmo em altas produtividades, pois a fixação biológica supre a demanda. Se a inoculação não for confirmada, calcula-se uma dose plena por exportação/eficiência (fórmula igual à do milho) como contingência.</t>
+      <c r="B29" s="31" t="inlineStr">
+        <is>
+          <t>Fonte/Confiança: Alta - Embrapa Soja (doutrina consolidada): soja bem inoculada com Bradyrhizobium não responde economicamente à adubação nitrogenada mineral, mesmo em altas produtividades, pois a fixação biológica supre a demanda. Se a inoculação não for confirmada, calcula-se uma dose plena por exportação/eficiência (fórmula igual à do milho) como contingência. Prêmissa editável em Dados de Entrada, seção 5.</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10610,7 @@
           <t>Exportação pela produtividade meta (kg/ha)</t>
         </is>
       </c>
-      <c r="C34" s="49">
+      <c r="C34" s="50">
         <f>C12*VLOOKUP("Soja",TAB_CULTURAS,6,FALSE)</f>
         <v/>
       </c>
@@ -10464,7 +10621,7 @@
           <t>Eficiência de aproveitamento do fertilizante (%)</t>
         </is>
       </c>
-      <c r="C35" s="59">
+      <c r="C35" s="60">
         <f>VLOOKUP(C9,TAB_EFICIENCIA,2,FALSE)</f>
         <v/>
       </c>
@@ -10475,7 +10632,7 @@
           <t>Dose de manutenção (exportação / eficiência), kg/ha</t>
         </is>
       </c>
-      <c r="C36" s="49">
+      <c r="C36" s="50">
         <f>C34/C35</f>
         <v/>
       </c>
@@ -10486,7 +10643,7 @@
           <t>Classe de fertilidade considerada</t>
         </is>
       </c>
-      <c r="C37" s="57">
+      <c r="C37" s="58">
         <f>C15</f>
         <v/>
       </c>
@@ -10497,18 +10654,18 @@
           <t>Fator de ajuste por classe (construção/manutenção/redução)</t>
         </is>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="45">
         <f>VLOOKUP(C15,TAB_FATOR_CLASSE,2,FALSE)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="41" t="inlineStr">
+      <c r="B39" s="42" t="inlineStr">
         <is>
           <t>Dose final de P2O5 (kg/ha)</t>
         </is>
       </c>
-      <c r="C39" s="58">
+      <c r="C39" s="59">
         <f>C36*C38</f>
         <v/>
       </c>
@@ -10519,13 +10676,13 @@
           <t>Total para a área (kg)</t>
         </is>
       </c>
-      <c r="C40" s="52">
+      <c r="C40" s="53">
         <f>C39*C6</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="30" t="inlineStr">
+      <c r="B41" s="31" t="inlineStr">
         <is>
           <t>Modelo: dose = (exportação pelo grão na produtividade meta / eficiência de aproveitamento pela textura) x fator de ajuste pela classe de fertilidade atual do solo. Não é uma tabela fixa - recalcula a cada mudança de solo, textura ou produtividade. Fonte dos coeficientes de exportação: ver aba BD Culturas. Confiança do fator de ajuste: Média (premissa transparente e editável).</t>
         </is>
@@ -10546,7 +10703,7 @@
           <t>Exportação pela produtividade meta (kg/ha)</t>
         </is>
       </c>
-      <c r="C46" s="49">
+      <c r="C46" s="50">
         <f>C12*VLOOKUP("Soja",TAB_CULTURAS,7,FALSE)</f>
         <v/>
       </c>
@@ -10557,7 +10714,7 @@
           <t>Eficiência de aproveitamento do fertilizante (%)</t>
         </is>
       </c>
-      <c r="C47" s="59">
+      <c r="C47" s="60">
         <f>VLOOKUP(C9,TAB_EFICIENCIA,3,FALSE)</f>
         <v/>
       </c>
@@ -10568,7 +10725,7 @@
           <t>Dose de manutenção (exportação / eficiência), kg/ha</t>
         </is>
       </c>
-      <c r="C48" s="49">
+      <c r="C48" s="50">
         <f>C46/C47</f>
         <v/>
       </c>
@@ -10579,7 +10736,7 @@
           <t>Classe de fertilidade considerada</t>
         </is>
       </c>
-      <c r="C49" s="57">
+      <c r="C49" s="58">
         <f>C16</f>
         <v/>
       </c>
@@ -10590,18 +10747,18 @@
           <t>Fator de ajuste por classe (construção/manutenção/redução)</t>
         </is>
       </c>
-      <c r="C50" s="44">
+      <c r="C50" s="45">
         <f>VLOOKUP(C16,TAB_FATOR_CLASSE,2,FALSE)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="41" t="inlineStr">
+      <c r="B51" s="42" t="inlineStr">
         <is>
           <t>Dose final de K2O (kg/ha)</t>
         </is>
       </c>
-      <c r="C51" s="58">
+      <c r="C51" s="59">
         <f>C48*C50</f>
         <v/>
       </c>
@@ -10612,13 +10769,13 @@
           <t>Total para a área (kg)</t>
         </is>
       </c>
-      <c r="C52" s="52">
+      <c r="C52" s="53">
         <f>C51*C6</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="30" t="inlineStr">
+      <c r="B53" s="31" t="inlineStr">
         <is>
           <t>Modelo: dose = (exportação pelo grão na produtividade meta / eficiência de aproveitamento pela textura) x fator de ajuste pela classe de fertilidade atual do solo. Não é uma tabela fixa - recalcula a cada mudança de solo, textura ou produtividade. Fonte dos coeficientes de exportação: ver aba BD Culturas. Confiança do fator de ajuste: Média (premissa transparente e editável).</t>
         </is>
@@ -10639,7 +10796,7 @@
           <t>Exportação de S pela produtividade meta (kg/ha)</t>
         </is>
       </c>
-      <c r="C58" s="49">
+      <c r="C58" s="50">
         <f>C12*VLOOKUP("Soja",TAB_CULTURAS,8,FALSE)</f>
         <v/>
       </c>
@@ -10647,11 +10804,12 @@
     <row r="59">
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Eficiência de aproveitamento do S (%) - padrão</t>
-        </is>
-      </c>
-      <c r="C59" s="60" t="n">
-        <v>0.6</v>
+          <t>Eficiência de aproveitamento do S (%) (Dados de Entrada)</t>
+        </is>
+      </c>
+      <c r="C59" s="61">
+        <f>'Dados de Entrada'!C52</f>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -10660,24 +10818,24 @@
           <t>Fator de ajuste por classe de S</t>
         </is>
       </c>
-      <c r="C60" s="44">
+      <c r="C60" s="45">
         <f>VLOOKUP(C19,TAB_FATOR_CLASSE,2,FALSE)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="41" t="inlineStr">
+      <c r="B61" s="42" t="inlineStr">
         <is>
           <t>Dose final de S (kg/ha)</t>
         </is>
       </c>
-      <c r="C61" s="58">
+      <c r="C61" s="59">
         <f>C58/C59*C60</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="43" t="inlineStr">
+      <c r="B62" s="44" t="inlineStr">
         <is>
           <t>Parte do S já pode ser suprida via gesso agrícola (ver aba Gessagem) - evitar dupla contagem ao montar a mistura final.</t>
         </is>
@@ -10696,7 +10854,7 @@
           <t>Exportação de Ca pela produtividade meta (kg/ha)</t>
         </is>
       </c>
-      <c r="C65" s="49">
+      <c r="C65" s="50">
         <f>C12*VLOOKUP("Soja",TAB_CULTURAS,9,FALSE)</f>
         <v/>
       </c>
@@ -10707,13 +10865,13 @@
           <t>Exportação de Mg pela produtividade meta (kg/ha)</t>
         </is>
       </c>
-      <c r="C66" s="49">
+      <c r="C66" s="50">
         <f>C12*VLOOKUP("Soja",TAB_CULTURAS,10,FALSE)</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="43" t="inlineStr">
+      <c r="B67" s="44" t="inlineStr">
         <is>
           <t>Ver abas Calagem e Gessagem para a recomendação de correção de Ca e Mg via calcário/gesso.</t>
         </is>
@@ -10732,7 +10890,7 @@
           <t>Zn - dose via solo (kg/ha produto puro)</t>
         </is>
       </c>
-      <c r="C70" s="44">
+      <c r="C70" s="45">
         <f>IFERROR(VLOOKUP("Zn|"&amp;C20,TAB_MICRO_DOSE,4,FALSE),0)</f>
         <v/>
       </c>
@@ -10743,7 +10901,7 @@
           <t>B - dose via solo (kg/ha produto puro)</t>
         </is>
       </c>
-      <c r="C71" s="44">
+      <c r="C71" s="45">
         <f>IFERROR(VLOOKUP("B|"&amp;C21,TAB_MICRO_DOSE,4,FALSE),0)</f>
         <v/>
       </c>
@@ -10754,7 +10912,7 @@
           <t>Cu - dose via solo (kg/ha produto puro)</t>
         </is>
       </c>
-      <c r="C72" s="44">
+      <c r="C72" s="45">
         <f>IFERROR(VLOOKUP("Cu|"&amp;C22,TAB_MICRO_DOSE,4,FALSE),0)</f>
         <v/>
       </c>
@@ -10765,7 +10923,7 @@
           <t>Mn - dose via solo (kg/ha produto puro)</t>
         </is>
       </c>
-      <c r="C73" s="44">
+      <c r="C73" s="45">
         <f>IFERROR(VLOOKUP("Mn|"&amp;C23,TAB_MICRO_DOSE,4,FALSE),0)</f>
         <v/>
       </c>
@@ -10776,7 +10934,7 @@
           <t>Mo - dose via solo (kg/ha produto puro)</t>
         </is>
       </c>
-      <c r="C74" s="44">
+      <c r="C74" s="45">
         <f>IFERROR(VLOOKUP("Mo|"&amp;C24,TAB_MICRO_DOSE,4,FALSE),0)</f>
         <v/>
       </c>
@@ -10811,11 +10969,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="C78" s="44">
+      <c r="C78" s="45">
         <f>C28</f>
         <v/>
       </c>
-      <c r="D78" s="52">
+      <c r="D78" s="53">
         <f>C28*C6</f>
         <v/>
       </c>
@@ -10826,11 +10984,11 @@
           <t>P2O5</t>
         </is>
       </c>
-      <c r="C79" s="44">
+      <c r="C79" s="45">
         <f>C39</f>
         <v/>
       </c>
-      <c r="D79" s="52">
+      <c r="D79" s="53">
         <f>C39*C6</f>
         <v/>
       </c>
@@ -10841,11 +10999,11 @@
           <t>K2O</t>
         </is>
       </c>
-      <c r="C80" s="44">
+      <c r="C80" s="45">
         <f>C51</f>
         <v/>
       </c>
-      <c r="D80" s="52">
+      <c r="D80" s="53">
         <f>C51*C6</f>
         <v/>
       </c>
@@ -10856,11 +11014,11 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C81" s="44">
+      <c r="C81" s="45">
         <f>C61</f>
         <v/>
       </c>
-      <c r="D81" s="52">
+      <c r="D81" s="53">
         <f>C61*C6</f>
         <v/>
       </c>
@@ -10871,11 +11029,11 @@
           <t>Zn</t>
         </is>
       </c>
-      <c r="C82" s="44">
+      <c r="C82" s="45">
         <f>C70</f>
         <v/>
       </c>
-      <c r="D82" s="52">
+      <c r="D82" s="53">
         <f>C70*C6</f>
         <v/>
       </c>
@@ -10886,11 +11044,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="C83" s="44">
+      <c r="C83" s="45">
         <f>C71</f>
         <v/>
       </c>
-      <c r="D83" s="52">
+      <c r="D83" s="53">
         <f>C71*C6</f>
         <v/>
       </c>
@@ -10901,11 +11059,11 @@
           <t>Cu</t>
         </is>
       </c>
-      <c r="C84" s="44">
+      <c r="C84" s="45">
         <f>C72</f>
         <v/>
       </c>
-      <c r="D84" s="52">
+      <c r="D84" s="53">
         <f>C72*C6</f>
         <v/>
       </c>
@@ -10916,11 +11074,11 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="C85" s="44">
+      <c r="C85" s="45">
         <f>C73</f>
         <v/>
       </c>
-      <c r="D85" s="52">
+      <c r="D85" s="53">
         <f>C73*C6</f>
         <v/>
       </c>
@@ -10931,11 +11089,11 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="C86" s="44">
+      <c r="C86" s="45">
         <f>C74</f>
         <v/>
       </c>
-      <c r="D86" s="52">
+      <c r="D86" s="53">
         <f>C74*C6</f>
         <v/>
       </c>
@@ -10959,11 +11117,6 @@
     <mergeCell ref="B33:G33"/>
     <mergeCell ref="B69:G69"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Sim,Não"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>